--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -3333,7 +3333,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PM-01</t>
+          <t>CH-11</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -3343,17 +3343,17 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>보험료납입/자동이체</t>
+          <t>보험금청구/신청</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>보험료 납입 관리</t>
+          <t>연금전환 사전신청</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>입금</t>
+          <t>신청</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>계약자(종신보험)</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -3373,40 +3373,44 @@
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>납입 대상 회차, 미납·연체 여부, 납입금액, 선납 할인</t>
-        </is>
-      </c>
-      <c r="J37" s="45" t="inlineStr">
-        <is>
-          <t>계약 선택, 납입 회차, 납입방법(계좌출금·가상계좌) / 납입 방법이 가상계좌면 발급 은행 선택(iM뱅크·농협), 내 계좌 출금이면 출금 계좌 선택</t>
-        </is>
-      </c>
-      <c r="K37" s="32" t="inlineStr">
-        <is>
-          <t>납입 완료 안내 / 가상계좌: 인증 후 「가상계좌 정보」(은행명·가상계좌번호(복사 버튼)·예금주명 「iM라이프」) + 이용안내(유효시간 내 입금, 입금 유효기간 신청일 오후 6시까지, 미입금 시 가상계좌 자동 폐기)</t>
+          <t>전환 가능 종신보험(적립금), 전환 시점 예상 적립금·연금액(예시)</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>대상 계약, 연금 전환 나이, 연금 유형, 지급 주기, 연금 받을 계좌</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>사전신청 접수·전환 예정일 30일 전 알림톡 안내</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>수금</t>
+          <t>보전</t>
         </is>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N37" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O37" s="10" t="n"/>
+          <t>사망보장 소멸·감소 안내</t>
+        </is>
+      </c>
+      <c r="N37" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="O37" s="10" t="inlineStr">
+        <is>
+          <t>v3.7 신규: 전환 예정일 전까지 변경·취소 가능 / v3.7: 2Depth 「보험계약관리」→「보험금청구/신청」 이동(연금 지급 신청 다음), 메뉴ID 유지</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>PM-02</t>
+          <t>PM-01</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -3421,17 +3425,17 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>보험료 자동이체 관리</t>
+          <t>보험료 납입 관리</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>입금</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>T4 단일폼 변경</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -3441,22 +3445,22 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>현재 이체 은행·계좌·이체일</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr">
-        <is>
-          <t>은행, 계좌, 이체일</t>
-        </is>
-      </c>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>변경 완료 알림</t>
+          <t>납입 대상 회차, 미납·연체 여부, 납입금액, 선납 할인</t>
+        </is>
+      </c>
+      <c r="J38" s="45" t="inlineStr">
+        <is>
+          <t>계약 선택, 납입 회차, 납입방법(계좌출금·가상계좌) / 납입 방법이 가상계좌면 발급 은행 선택(iM뱅크·농협), 내 계좌 출금이면 출금 계좌 선택</t>
+        </is>
+      </c>
+      <c r="K38" s="32" t="inlineStr">
+        <is>
+          <t>납입 완료 안내 / 가상계좌: 인증 후 「가상계좌 정보」(은행명·가상계좌번호(복사 버튼)·예금주명 「iM라이프」) + 이용안내(유효시간 내 입금, 입금 유효기간 신청일 오후 6시까지, 미입금 시 가상계좌 자동 폐기)</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
@@ -3464,9 +3468,9 @@
           <t>수금</t>
         </is>
       </c>
-      <c r="M38" s="11" t="inlineStr">
-        <is>
-          <t>출금 동의(전자서명)</t>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="14" t="inlineStr">
@@ -3479,7 +3483,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>PM-03</t>
+          <t>PM-02</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -3494,7 +3498,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>보험료 자동대출납입 신청/취소</t>
+          <t>보험료 자동이체 관리</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -3514,22 +3518,22 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>신청 여부, 대출 가능금액, 적용이율</t>
+          <t>현재 이체 은행·계좌·이체일</t>
         </is>
       </c>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>신청·취소</t>
+          <t>은행, 계좌, 이체일</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 안내</t>
+          <t>변경 완료 알림</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
@@ -3539,12 +3543,12 @@
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>대출 이자 발생 고지</t>
-        </is>
-      </c>
-      <c r="N39" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
+          <t>출금 동의(전자서명)</t>
+        </is>
+      </c>
+      <c r="N39" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
         </is>
       </c>
       <c r="O39" s="10" t="n"/>
@@ -3552,7 +3556,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>PM-04</t>
+          <t>PM-03</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -3567,22 +3571,22 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>유니버설 자유납입 관리</t>
+          <t>보험료 자동대출납입 신청/취소</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>입금</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T4 단일폼 변경</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>유니버설 계약자</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
@@ -3592,17 +3596,17 @@
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>추가납입 한도·잔여 한도, 납입 일시중지 가능 여부</t>
+          <t>신청 여부, 대출 가능금액, 적용이율</t>
         </is>
       </c>
       <c r="J40" s="13" t="inlineStr">
         <is>
-          <t>추가납입 금액, 일시중지 신청</t>
+          <t>신청·취소</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>처리 완료 안내</t>
+          <t>변경 완료 안내</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
@@ -3612,12 +3616,12 @@
       </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
-          <t>납입중지 시 월대체보험료 차감 고지</t>
-        </is>
-      </c>
-      <c r="N40" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
+          <t>대출 이자 발생 고지</t>
+        </is>
+      </c>
+      <c r="N40" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
       <c r="O40" s="10" t="n"/>
@@ -3625,7 +3629,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>CH-10</t>
+          <t>PM-04</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -3635,17 +3639,17 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>보험계약관리</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>계약관계자변경</t>
+          <t>보험료납입/자동이체</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>유니버설 자유납입 관리</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>입금</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
@@ -3655,37 +3659,37 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>계약자(피보험자 동의 필요)</t>
+          <t>유니버설 계약자</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>현재 수익자(만기·사망·기타)</t>
+          <t>추가납입 한도·잔여 한도, 납입 일시중지 가능 여부</t>
         </is>
       </c>
       <c r="J41" s="13" t="inlineStr">
         <is>
-          <t>변경 수익자 정보, 피보험자 동의</t>
+          <t>추가납입 금액, 일시중지 신청</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 안내</t>
+          <t>처리 완료 안내</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>보전</t>
+          <t>수금</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>사망수익자 변경 시 피보험자 동의(상법)</t>
+          <t>납입중지 시 월대체보험료 차감 고지</t>
         </is>
       </c>
       <c r="N41" s="14" t="inlineStr">
@@ -3698,7 +3702,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>CH-05</t>
+          <t>CH-10</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -3711,9 +3715,9 @@
           <t>보험계약관리</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>보험기간/연금개시연도 변경</t>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>계약관계자변경</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -3728,22 +3732,22 @@
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>계약자(피보험자 동의 필요)</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>연금 계약 카드(현재 연금개시 나이·일자, 납입 현황, 적립금), 변경 가능 범위(55~80세)</t>
+          <t>현재 수익자(만기·사망·기타)</t>
         </is>
       </c>
       <c r="J42" s="13" t="inlineStr">
         <is>
-          <t>대상 계약(카드 라디오 선택), 변경 후 연금개시 나이</t>
+          <t>변경 수익자 정보, 피보험자 동의</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
@@ -3756,26 +3760,22 @@
           <t>보전</t>
         </is>
       </c>
-      <c r="M42" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N42" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O42" s="10" t="inlineStr">
-        <is>
-          <t>선택 → 입력 → 인증 → 완료 (확인 단계 생략)</t>
-        </is>
-      </c>
+      <c r="M42" s="11" t="inlineStr">
+        <is>
+          <t>사망수익자 변경 시 피보험자 동의(상법)</t>
+        </is>
+      </c>
+      <c r="N42" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>CH-07</t>
+          <t>CH-05</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>연금개시유형 선택/변경</t>
+          <t>보험기간/연금개시연도 변경</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>연금 계약자</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -3813,14 +3813,14 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I43" s="32" t="inlineStr">
-        <is>
-          <t>연금 계약(선택 단계), 선택 요약·월 환산 예상액·회당 예상 연금액(지급주기 반영, 예시)</t>
-        </is>
-      </c>
-      <c r="J43" s="32" t="inlineStr">
-        <is>
-          <t>연금유형, 개인형/부부형, 연금비율, 체증형태, 체증기간, 체증율, 확정기간, 보증기간, 지급주기, 조기집중형보장배수 (10개 선택조건)</t>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>연금 계약 카드(현재 연금개시 나이·일자, 납입 현황, 적립금), 변경 가능 범위(55~80세)</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>대상 계약(카드 라디오 선택), 변경 후 연금개시 나이</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -3833,26 +3833,26 @@
           <t>보전</t>
         </is>
       </c>
-      <c r="M43" s="33" t="inlineStr">
-        <is>
-          <t>개시 후 변경 제한 고지 / 예상 연금액은 예시(확정 아님)</t>
-        </is>
-      </c>
-      <c r="N43" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O43" s="34" t="inlineStr">
-        <is>
-          <t>v3.3: 연금유형별 고정값 규칙 적용(상세: 「선택조건_CH-07」 시트) · 고정 항목은 고정값만 표시·선택 불가 · 입력 영역 PC 2열/모바일 2열(긴 항목 1열) 촘촘한 버튼형 배치</t>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="O43" s="10" t="inlineStr">
+        <is>
+          <t>선택 → 입력 → 인증 → 완료 (확인 단계 생략)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>CH-11</t>
+          <t>CH-07</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>연금전환 사전신청</t>
+          <t>연금개시유형 선택/변경</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>신청</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>계약자(종신보험)</t>
+          <t>연금 계약자</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -3890,19 +3890,19 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>전환 가능 종신보험(적립금), 전환 시점 예상 적립금·연금액(예시)</t>
-        </is>
-      </c>
-      <c r="J44" s="13" t="inlineStr">
-        <is>
-          <t>대상 계약, 연금 전환 나이, 연금 유형, 지급 주기, 연금 받을 계좌</t>
+      <c r="I44" s="32" t="inlineStr">
+        <is>
+          <t>연금 계약(선택 단계), 선택 요약·월 환산 예상액·회당 예상 연금액(지급주기 반영, 예시)</t>
+        </is>
+      </c>
+      <c r="J44" s="32" t="inlineStr">
+        <is>
+          <t>연금유형, 개인형/부부형, 연금비율, 체증형태, 체증기간, 체증율, 확정기간, 보증기간, 지급주기, 조기집중형보장배수 (10개 선택조건)</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>사전신청 접수·전환 예정일 30일 전 알림톡 안내</t>
+          <t>변경 완료 안내</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
@@ -3910,19 +3910,19 @@
           <t>보전</t>
         </is>
       </c>
-      <c r="M44" s="10" t="inlineStr">
-        <is>
-          <t>사망보장 소멸·감소 안내</t>
-        </is>
-      </c>
-      <c r="N44" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O44" s="10" t="inlineStr">
-        <is>
-          <t>v3.7 신규: 전환 예정일 전까지 변경·취소 가능</t>
+      <c r="M44" s="33" t="inlineStr">
+        <is>
+          <t>개시 후 변경 제한 고지 / 예상 연금액은 예시(확정 아님)</t>
+        </is>
+      </c>
+      <c r="N44" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O44" s="34" t="inlineStr">
+        <is>
+          <t>v3.3: 연금유형별 고정값 규칙 적용(상세: 「선택조건_CH-07」 시트) · 고정 항목은 고정값만 표시·선택 불가 · 입력 영역 PC 2열/모바일 2열(긴 항목 1열) 촘촘한 버튼형 배치</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7502,6 +7502,33 @@
       <c r="E61" s="11" t="inlineStr">
         <is>
           <t>CH-11(신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>「연금전환 사전신청」 2Depth 「보험계약관리」 → 「보험금청구/신청」 이동, 「연금 지급 신청」 다음에 배치 (메뉴ID CH-11 유지)</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>CH-11</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="34" t="inlineStr">
         <is>
-          <t>PC 전용. 2Depth 옆 개수 미표시. A2 메뉴에 자물쇠 표시 / v3.6: 업무 화면 좌측 메뉴(PC) — 2Depth는 굵은 소제목(15px·청록 표시 막대)·그룹 사이 구분선, 3Depth는 들여쓰기 + 왼쪽 안내선으로 하위 메뉴 표시(현재 화면은 강조 배경·막대)</t>
+          <t>PC 전용. 2Depth 옆 개수 미표시. A2 메뉴에 자물쇠 표시 / v3.6: 업무 화면 좌측 메뉴(PC) — 2Depth는 굵은 소제목(15px·청록 표시 막대)·그룹 사이 구분선, 3Depth는 들여쓰기 + 왼쪽 안내선으로 하위 메뉴 표시(현재 화면은 강조 배경·막대) / v3.7: Esc로 메가메뉴를 닫으면 주메뉴로 초점 복귀(다시 열리지 않음)</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>화면 이동 시 초점을 화면 제목으로, 단계 이동 시 현재 단계로 이동 / 대화상자 초점 가두기·Esc 닫기·초점 복귀 / 오류 시 첫 오류 칸으로 초점 이동</t>
+          <t>화면 이동 시 초점을 화면 제목으로, 단계 이동 시 현재 단계로 이동 / 대화상자 초점 가두기·Esc 닫기(인증 대기 중 제외)·초점 복귀 / 오류 시 첫 오류 칸으로 초점 이동</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="O14" s="34" t="inlineStr">
         <is>
-          <t>v3.1: 우편을 자택·직장으로 분리, 선택 안내장에만 「받지 않음」 제공 / 전자적방법 수신동의 문구: 「보험서비스에 관련된 안내장을 전자적방법(이메일, 모바일 등)으로 수신하는 것에 동의 합니다.」 — 이메일 항목 다음 배치 / 연동: ① 모바일·이메일 선택 시 수신동의 자동 체크 ② 수신동의 해제 시 확인 레이어팝업(우측 상단 X 닫기, 하단 [아니오][예]) 「전자적방법 수신동의 체크 해제 시 안내장별 수신 방법을 우편으로 선택하셔야 합니다. 해제하시겠습니까?」 → 예: 모바일·이메일 수신 안내장을 우편(자택)으로 변경 후 해제 / 아니오·X: 팝업만 닫고 동의 유지</t>
+          <t>v3.1: 우편을 자택·직장으로 분리, 선택 안내장에만 「받지 않음」 제공 / 전자적방법 수신동의 문구: 「보험서비스에 관련된 안내장을 전자적방법(이메일, 모바일 등)으로 수신하는 것에 동의 합니다.」 — 이메일 항목 다음 배치 / 연동: ① 모바일·이메일 선택 시 수신동의 자동 체크 ② 수신동의 해제 시 확인 레이어팝업(우측 상단 X 닫기, 하단 [아니오][예]) 「전자적방법 수신동의 체크 해제 시 안내장별 수신 방법을 우편으로 선택하셔야 합니다. 해제하시겠습니까?」 → 예: 모바일·이메일 수신 안내장을 우편(자택)으로 변경 후 해제 / 아니오·X·Esc: 팝업만 닫고 동의 유지</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7529,6 +7529,114 @@
       <c r="E62" s="11" t="inlineStr">
         <is>
           <t>CH-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>프로토타입 구현 기술을 React + TypeScript로 전환 (화면 구성·업무 흐름·입력 규칙 변경 없음 — 전환 전후 화면 구조 비교 테스트로 확인)</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>전체(프로토타입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>GNB 메가메뉴: Esc로 닫은 뒤 주메뉴로 초점이 돌아올 때 메가메뉴가 다시 열리던 문제 수정</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>CM-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>대화상자 공통: 인증 대기 중에는 Esc로 닫히지 않음 명시</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>CM-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>전자적방법 수신동의 해제 확인 팝업: Esc로 닫아도 「아니오」와 같이 동의 유지</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>MY-02</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
-          <t>메인 상단 [바로가기 추가] 버튼(모바일은 안내 문구와 한 줄·작은 버튼). 원클릭 설치는 운영 HTTPS+웹앱 매니페스트 필요</t>
+          <t>메인 상단 [바로가기 추가] 버튼(모바일은 안내 문구와 한 줄·작은 버튼). 원클릭 설치는 운영 HTTPS+웹앱 매니페스트 필요 / v3.7: 바로가기 파일은 지금 보고 있는 사이버창구 주소를 연다(설정 주소는 알 수 없을 때만)</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7637,6 +7637,33 @@
       <c r="E66" s="11" t="inlineStr">
         <is>
           <t>MY-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>바로가기 추가: 바로가기 파일이 지금 보고 있는 사이버창구 주소를 열도록 수정(운영 예정 주소로 열리던 문제)</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>CM-07</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -1449,7 +1449,7 @@
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>PC: 바탕화면 바로가기 파일(.url/.webloc) 다운로드 / 모바일: 홈 화면 추가 안내</t>
+          <t>PC: 바탕화면 바로가기 파일 다운로드(Windows .url 을 zip 에 담아 / Mac .webloc) / 모바일: 홈 화면 추가 안내</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
-          <t>메인 상단 [바로가기 추가] 버튼(모바일은 안내 문구와 한 줄·작은 버튼). 원클릭 설치는 운영 HTTPS+웹앱 매니페스트 필요 / v3.7: 바로가기 파일은 지금 보고 있는 사이버창구 주소를 연다(설정 주소는 알 수 없을 때만)</t>
+          <t>메인 상단 [바로가기 추가] 버튼(모바일은 안내 문구와 한 줄·작은 버튼). 원클릭 설치는 운영 HTTPS+웹앱 매니페스트 필요 / v3.7: 바로가기 파일은 지금 보고 있는 사이버창구 주소를 연다(설정 주소는 알 수 없을 때만) / v3.7: 크롬·엣지가 .url 을 .download 로 바꿔 저장하므로 Windows 는 zip(압축 파일) 안에 .url 로 제공, Mac .webloc 은 확장자가 덧붙지 않게 저장</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7662,6 +7662,33 @@
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>CM-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>바로가기 추가: Windows 바로가기를 zip 에 담아 제공(.url.download 로 저장되던 문제), Mac .webloc 저장 형식 정리, 안내 문구 갱신</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
         <is>
           <t>CM-07</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -2069,7 +2069,7 @@
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
-          <t>v3.1: 계약별 대출 가능금액 = 대출 한도 − 기존 대출잔액</t>
+          <t>v3.1: 계약별 대출 가능금액 = 대출 한도 − 기존 대출잔액 / v3.7: 계약 카드 [계약상세]는 해당 계약의 계약조회 상세로 바로 이동</t>
         </is>
       </c>
     </row>
@@ -2116,12 +2116,12 @@
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>기본계약사항, 주계약·특약별 보장내용·가입금액, 계약관계자, 납입정보, 약관·안내장 목록</t>
+          <t>보유계약 카드(상품명·증권번호·피보험자·계약상태·월보험료·계약일·보험기간·납입현황), 카드 선택 시 기본계약사항, 주계약·특약별 보장내용·가입금액, 계약관계자, 납입정보, 약관·안내장 목록</t>
         </is>
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
-          <t>계약 선택</t>
+          <t>계약 카드 선택</t>
         </is>
       </c>
       <c r="K20" s="15" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="O20" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 계약별 약관·보험상품안내장(가입 당시 기준, 각 1건) PDF 다운로드</t>
+          <t>v3.7: 계약별 약관·보험상품안내장(가입 당시 기준, 각 1건) PDF 다운로드 / v3.7: 첫 화면을 계약종합현황과 같은 카드 형식으로 변경 — [상세 보기]로 계약 상세 진입, [계약 목록]으로 카드 목록 복귀(보던 카드로 초점)</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7691,6 +7691,60 @@
       <c r="E68" s="11" t="inlineStr">
         <is>
           <t>CM-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>계약조회 첫 화면을 보유계약 카드(계약종합현황 형식)로 변경, 카드 선택 시 계약 상세·[계약 목록]으로 복귀(계약 탭 삭제)</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>CT-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>계약종합현황 [계약상세]: 해당 계약의 계약조회 상세로 바로 이동</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>CT-01</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -2193,12 +2193,12 @@
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
-          <t>적립금, 펀드별 편입비율·수익률, 누적 수익률</t>
+          <t>변액 계약 카드(상품명·증권번호·피보험자·계약상태·적립금·누적 수익률·납입 원금·편입 펀드), 카드 선택 시 적립금, 펀드별 편입비율·수익률, 누적 수익률</t>
         </is>
       </c>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>조회기간</t>
+          <t>변액 계약 카드 선택, 조회기간</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="O21" s="34" t="inlineStr">
         <is>
-          <t>변액 계약이 2건 이상이면 상단 계약 탭으로 선택(변액보험 조회·펀드변경 간 선택 유지, 계약카드 「펀드 수익률」에서 진입 시 해당 계약 선택)</t>
+          <t>v3.7: 첫 화면을 변액 계약 카드(계약조회와 같은 형식)로 변경 — [상세 보기]로 적립금·펀드 목록, [계약 목록]으로 카드 목록 복귀(보던 카드로 초점), 상단 계약 탭 삭제 / 고른 계약은 펀드변경과 공유, 계약종합현황 「펀드 수익률」에서 진입 시 해당 계약 상세 바로 표시</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7745,6 +7745,33 @@
       <c r="E70" s="11" t="inlineStr">
         <is>
           <t>CT-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>변액보험 조회 첫 화면을 변액 계약 카드로 변경, 카드 선택 시 적립금·펀드 목록·[계약 목록]으로 복귀(계약 탭 삭제), 계약종합현황 「펀드 수익률」은 해당 계약 상세로 바로 이동</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>CT-03</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적합성진단_CH-01" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'메뉴정의서'!$A$4:$O$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'메뉴정의서'!$A$4:$O$65</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -823,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -853,7 +853,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>61개 화면(업무 53 + 공통 8) · v3.7 · 메뉴명=공개 사이트맵 확인 / 공통(CM)=프로토타입 v3.7 반영 / 회색 글씨 항목=추정(로그인 화면 미확인) / 메뉴ID: 업무코드-번호 (CM 공통 · MY · CT · PY · PM · CH · LN · CF · CS 서류·안내)</t>
+          <t>62개 화면(업무 53 + 공통 9) · v3.7 · 메뉴명=공개 사이트맵 확인 / 공통(CM)=프로토타입 v3.7 반영 / 회색 글씨 항목=추정(로그인 화면 미확인) / 메뉴ID: 업무코드-번호 (CM 공통 · MY · CT · PY · PM · CH · LN · CF · CS 서류·안내)</t>
         </is>
       </c>
     </row>
@@ -1553,32 +1553,32 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>MY-01</t>
+          <t>CM-09</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>MyPage</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>개인정보관리</t>
+          <t>계좌</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>개인정보변경</t>
+          <t>다른 본인 계좌 등록</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>신청</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>T4 단일폼 변경</t>
+          <t>T0 공통영역</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1593,17 +1593,17 @@
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>현재 주소(자택·직장), 휴대폰·자택·직장 전화, 이메일</t>
+          <t>예금주(본인 이름 고정), 은행 목록, 계좌번호, 계좌 확인 결과(예금주·본인 확인 완료 / 실패 사유)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t>자택/회사 주소(우편번호 검색), 전화번호, 휴대폰, 이메일</t>
+          <t>은행, 계좌번호(숫자 10~14자리, - 허용)</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 안내(변경 전 연락처로도 통지)</t>
+          <t>[계좌 확인]: 은행 예금주 조회로 계좌 존재·본인 명의 확인 → 확인 성공 시에만 [등록] → 등록 계좌가 계좌 목록에 추가·선택(마스킹 표시) / 취소·Esc: 직전에 고른 계좌 유지</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
@@ -1613,24 +1613,24 @@
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>개인정보 변경 사실 통지</t>
-        </is>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
+          <t>본인 명의 계좌만 등록(예금주 불일치 시 등록 불가)</t>
+        </is>
+      </c>
+      <c r="N13" s="30" t="inlineStr">
+        <is>
+          <t>미확인</t>
         </is>
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
-          <t>변경한 연락처는 보유 계약 전체에 일괄 적용 (적용할 계약 선택 항목 없음)</t>
+          <t>v3.7 신규: 출금·입금 계좌 선택칸에서 「다른 본인 계좌 등록」 선택 시 레이어팝업(PM-01 등 계좌 선택칸이 있는 모든 화면 공통) / 계좌 확인 전 [등록] 시 「계좌 확인을 먼저 해 주세요」, 확인 후 은행·계좌번호를 바꾸면 다시 확인 / 이미 등록된 계좌 중복 등록 불가 / 「다른 본인 계좌 등록」이 선택된 채로는 다음 단계 진행 불가 / 프로토타입은 은행 조회 시뮬레이션(끝자리 000: 없는 계좌, 999: 타인 명의)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>MY-02</t>
+          <t>MY-01</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>안내장수신설정</t>
+          <t>개인정보변경</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>로그인 고객</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -1668,29 +1668,29 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I14" s="32" t="inlineStr">
-        <is>
-          <t>안내장 종류별 현재 수신방법, 안내장 받으실 곳(휴대폰·이메일), 전자적방법 수신동의 여부</t>
-        </is>
-      </c>
-      <c r="J14" s="32" t="inlineStr">
-        <is>
-          <t>안내장별 수신방법(모바일·이메일·우편(자택)·우편(직장)·받지 않음), 전자적방법 수신동의(체크박스 선택·해제)</t>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>현재 주소(자택·직장), 휴대폰·자택·직장 전화, 이메일</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>자택/회사 주소(우편번호 검색), 전화번호, 휴대폰, 이메일</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 안내</t>
+          <t>변경 완료 안내(변경 전 연락처로도 통지)</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>안내장</t>
-        </is>
-      </c>
-      <c r="M14" s="33" t="inlineStr">
-        <is>
-          <t>법정 안내장은 수신 거부 불가 — 구분이 「법정」이면 수신방법 목록에 「받지 않음」 미노출 / 수신방법에 모바일·이메일이 하나라도 있으면 전자적방법 수신동의 필수</t>
+          <t>고객</t>
+        </is>
+      </c>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>개인정보 변경 사실 통지</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
@@ -1698,16 +1698,16 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O14" s="34" t="inlineStr">
-        <is>
-          <t>v3.1: 우편을 자택·직장으로 분리, 선택 안내장에만 「받지 않음」 제공 / 전자적방법 수신동의 문구: 「보험서비스에 관련된 안내장을 전자적방법(이메일, 모바일 등)으로 수신하는 것에 동의 합니다.」 — 이메일 항목 다음 배치 / 연동: ① 모바일·이메일 선택 시 수신동의 자동 체크 ② 수신동의 해제 시 확인 레이어팝업(우측 상단 X 닫기, 하단 [아니오][예]) 「전자적방법 수신동의 체크 해제 시 안내장별 수신 방법을 우편으로 선택하셔야 합니다. 해제하시겠습니까?」 → 예: 모바일·이메일 수신 안내장을 우편(자택)으로 변경 후 해제 / 아니오·X·Esc: 팝업만 닫고 동의 유지</t>
+      <c r="O14" s="10" t="inlineStr">
+        <is>
+          <t>변경한 연락처는 보유 계약 전체에 일괄 적용 (적용할 계약 선택 항목 없음)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>MY-03</t>
+          <t>MY-02</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>마케팅동의 및 철회</t>
+          <t>안내장수신설정</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>로그인 고객</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -1745,14 +1745,14 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>동의 항목별 상태·동의일</t>
-        </is>
-      </c>
-      <c r="J15" s="21" t="inlineStr">
-        <is>
-          <t>동의·철회, 연락 채널 선택(우편·이메일·모바일)</t>
+      <c r="I15" s="32" t="inlineStr">
+        <is>
+          <t>안내장 종류별 현재 수신방법, 안내장 받으실 곳(휴대폰·이메일), 전자적방법 수신동의 여부</t>
+        </is>
+      </c>
+      <c r="J15" s="32" t="inlineStr">
+        <is>
+          <t>안내장별 수신방법(모바일·이메일·우편(자택)·우편(직장)·받지 않음), 전자적방법 수신동의(체크박스 선택·해제)</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>고객</t>
-        </is>
-      </c>
-      <c r="M15" s="11" t="inlineStr">
-        <is>
-          <t>개인정보보호법·신용정보법</t>
+          <t>안내장</t>
+        </is>
+      </c>
+      <c r="M15" s="33" t="inlineStr">
+        <is>
+          <t>법정 안내장은 수신 거부 불가 — 구분이 「법정」이면 수신방법 목록에 「받지 않음」 미노출 / 수신방법에 모바일·이메일이 하나라도 있으면 전자적방법 수신동의 필수</t>
         </is>
       </c>
       <c r="N15" s="14" t="inlineStr">
@@ -1775,12 +1775,16 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O15" s="10" t="n"/>
+      <c r="O15" s="34" t="inlineStr">
+        <is>
+          <t>v3.1: 우편을 자택·직장으로 분리, 선택 안내장에만 「받지 않음」 제공 / 전자적방법 수신동의 문구: 「보험서비스에 관련된 안내장을 전자적방법(이메일, 모바일 등)으로 수신하는 것에 동의 합니다.」 — 이메일 항목 다음 배치 / 연동: ① 모바일·이메일 선택 시 수신동의 자동 체크 ② 수신동의 해제 시 확인 레이어팝업(우측 상단 X 닫기, 하단 [아니오][예]) 「전자적방법 수신동의 체크 해제 시 안내장별 수신 방법을 우편으로 선택하셔야 합니다. 해제하시겠습니까?」 → 예: 모바일·이메일 수신 안내장을 우편(자택)으로 변경 후 해제 / 아니오·X·Esc: 팝업만 닫고 동의 유지</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>MY-04</t>
+          <t>MY-03</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -1795,17 +1799,17 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>신용정보 이용·제공 내역</t>
+          <t>마케팅동의 및 철회</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>T2 목록+상세</t>
+          <t>T4 단일폼 변경</t>
         </is>
       </c>
       <c r="G16" s="11" t="inlineStr">
@@ -1820,17 +1824,17 @@
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>이용·제공 주체, 일자, 목적, 내용, 보유기간</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
-        <is>
-          <t>조회기간</t>
-        </is>
-      </c>
-      <c r="K16" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>동의 항목별 상태·동의일</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>동의·철회, 연락 채널 선택(우편·이메일·모바일)</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>변경 완료 안내</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
@@ -1840,7 +1844,7 @@
       </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
-          <t>신용정보법 – 이용·제공 내역 조회권</t>
+          <t>개인정보보호법·신용정보법</t>
         </is>
       </c>
       <c r="N16" s="14" t="inlineStr">
@@ -1853,7 +1857,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>MY-05</t>
+          <t>MY-04</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -1868,17 +1872,17 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>고객확인제도</t>
+          <t>신용정보 이용·제공 내역</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>신청</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T2 목록+상세</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -1893,17 +1897,17 @@
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
-          <t>고객확인 상태, 재확인 기한</t>
+          <t>이용·제공 주체, 일자, 목적, 내용, 보유기간</t>
         </is>
       </c>
       <c r="J17" s="13" t="inlineStr">
         <is>
-          <t>직업·직장, 거래목적, 자금원천, 실제소유자 확인 등</t>
-        </is>
-      </c>
-      <c r="K17" s="13" t="inlineStr">
-        <is>
-          <t>확인 완료 안내</t>
+          <t>조회기간</t>
+        </is>
+      </c>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -1913,20 +1917,20 @@
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>특정금융정보법(KYC·자금세탁방지)</t>
-        </is>
-      </c>
-      <c r="N17" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O17" s="11" t="n"/>
+          <t>신용정보법 – 이용·제공 내역 조회권</t>
+        </is>
+      </c>
+      <c r="N17" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>MY-07</t>
+          <t>MY-05</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -1936,27 +1940,27 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>안내장 수신내역조회</t>
+          <t>개인정보관리</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>안내장 수신내역조회</t>
+          <t>고객확인제도</t>
         </is>
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>신청</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>T2 목록+상세</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>로그인 고객</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -1966,55 +1970,55 @@
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>발송일, 안내장명, 대상 계약, 수신방법, 안내장 열람(PDF)</t>
+          <t>고객확인 상태, 재확인 기한</t>
         </is>
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>조회기간·안내장 종류</t>
-        </is>
-      </c>
-      <c r="K18" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>직업·직장, 거래목적, 자금원천, 실제소유자 확인 등</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>확인 완료 안내</t>
         </is>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>안내장</t>
-        </is>
-      </c>
-      <c r="M18" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>고객</t>
+        </is>
+      </c>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>특정금융정보법(KYC·자금세탁방지)</t>
         </is>
       </c>
       <c r="N18" s="16" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O18" s="10" t="n"/>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="O18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>CT-01</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>보험</t>
+          <t>MY-07</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>MyPage</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>계약종합현황</t>
+          <t>안내장 수신내역조회</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>계약종합현황</t>
+          <t>안내장 수신내역조회</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -2024,12 +2028,12 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>T1 대시보드</t>
+          <t>T2 목록+상세</t>
         </is>
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>계약자·피보험자</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -2039,22 +2043,22 @@
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>보유계약 전체 목록, 계약상태, 월보험료, 납입현황, 예상 해지환급금, 대출 잔액</t>
-        </is>
-      </c>
-      <c r="J19" s="15" t="inlineStr">
+          <t>발송일, 안내장명, 대상 계약, 수신방법, 안내장 열람(PDF)</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>조회기간·안내장 종류</t>
+        </is>
+      </c>
+      <c r="K19" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K19" s="13" t="inlineStr">
-        <is>
-          <t>계약별 상세·업무 바로가기</t>
-        </is>
-      </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>보전</t>
+          <t>안내장</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr">
@@ -2062,21 +2066,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N19" s="14" t="inlineStr">
+      <c r="N19" s="16" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="O19" s="10" t="inlineStr">
-        <is>
-          <t>v3.1: 계약별 대출 가능금액 = 대출 한도 − 기존 대출잔액 / v3.7: 계약 카드 [계약상세]는 해당 계약의 계약조회 상세로 바로 이동</t>
-        </is>
-      </c>
+      <c r="O19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>CT-02</t>
+          <t>CT-01</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>보험계약조회</t>
+          <t>계약종합현황</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>계약조회</t>
+          <t>계약종합현황</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>T2 목록+상세</t>
+          <t>T1 대시보드</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -2116,17 +2116,17 @@
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>보유계약 카드(상품명·증권번호·피보험자·계약상태·월보험료·계약일·보험기간·납입현황), 카드 선택 시 기본계약사항, 주계약·특약별 보장내용·가입금액, 계약관계자, 납입정보, 약관·안내장 목록</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
-        <is>
-          <t>계약 카드 선택</t>
-        </is>
-      </c>
-      <c r="K20" s="15" t="inlineStr">
-        <is>
-          <t>약관·안내장 PDF 다운로드</t>
+          <t>보유계약 전체 목록, 계약상태, 월보험료, 납입현황, 예상 해지환급금, 대출 잔액</t>
+        </is>
+      </c>
+      <c r="J20" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>계약별 상세·업무 바로가기</t>
         </is>
       </c>
       <c r="L20" s="9" t="inlineStr">
@@ -2146,14 +2146,14 @@
       </c>
       <c r="O20" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 계약별 약관·보험상품안내장(가입 당시 기준, 각 1건) PDF 다운로드 / v3.7: 첫 화면을 계약종합현황과 같은 카드 형식으로 변경 — [상세 보기]로 계약 상세 진입, [계약 목록]으로 카드 목록 복귀(보던 카드로 초점)</t>
+          <t>v3.1: 계약별 대출 가능금액 = 대출 한도 − 기존 대출잔액 / v3.7: 계약 카드 [계약상세]는 해당 계약의 계약조회 상세로 바로 이동</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>CT-03</t>
+          <t>CT-02</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>변액보험 조회</t>
+          <t>계약조회</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>변액 계약자</t>
+          <t>계약자·피보험자</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -2193,17 +2193,17 @@
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
-          <t>변액 계약 카드(상품명·증권번호·피보험자·계약상태·적립금·누적 수익률·납입 원금·편입 펀드), 카드 선택 시 적립금, 펀드별 편입비율·수익률, 누적 수익률</t>
+          <t>보유계약 카드(상품명·증권번호·피보험자·계약상태·월보험료·계약일·보험기간·납입현황), 카드 선택 시 기본계약사항, 주계약·특약별 보장내용·가입금액, 계약관계자, 납입정보, 약관·안내장 목록</t>
         </is>
       </c>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>변액 계약 카드 선택, 조회기간</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>펀드변경 연결</t>
+          <t>계약 카드 선택</t>
+        </is>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>약관·안내장 PDF 다운로드</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -2211,9 +2211,9 @@
           <t>보전</t>
         </is>
       </c>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>투자손실 가능성 고지</t>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">
@@ -2221,16 +2221,16 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O21" s="34" t="inlineStr">
-        <is>
-          <t>v3.7: 첫 화면을 변액 계약 카드(계약조회와 같은 형식)로 변경 — [상세 보기]로 적립금·펀드 목록, [계약 목록]으로 카드 목록 복귀(보던 카드로 초점), 상단 계약 탭 삭제 / 고른 계약은 펀드변경과 공유, 계약종합현황 「펀드 수익률」에서 진입 시 해당 계약 상세 바로 표시</t>
+      <c r="O21" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 계약별 약관·보험상품안내장(가입 당시 기준, 각 1건) PDF 다운로드 / v3.7: 첫 화면을 계약종합현황과 같은 카드 형식으로 변경 — [상세 보기]로 계약 상세 진입, [계약 목록]으로 카드 목록 복귀(보던 카드로 초점)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>CT-04</t>
+          <t>CT-03</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>휴면보험금 조회</t>
+          <t>변액보험 조회</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>계약자·수익자</t>
+          <t>변액 계약자</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -2270,17 +2270,17 @@
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>휴면보험금 목록, 금액, 발생일</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>변액 계약 카드(상품명·증권번호·피보험자·계약상태·적립금·누적 수익률·납입 원금·편입 펀드), 카드 선택 시 적립금, 펀드별 편입비율·수익률, 누적 수익률</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>변액 계약 카드 선택, 조회기간</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>미수령보험금 신청 연결</t>
+          <t>펀드변경 연결</t>
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr">
@@ -2288,9 +2288,9 @@
           <t>보전</t>
         </is>
       </c>
-      <c r="M22" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>투자손실 가능성 고지</t>
         </is>
       </c>
       <c r="N22" s="14" t="inlineStr">
@@ -2298,12 +2298,16 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O22" s="10" t="n"/>
+      <c r="O22" s="34" t="inlineStr">
+        <is>
+          <t>v3.7: 첫 화면을 변액 계약 카드(계약조회와 같은 형식)로 변경 — [상세 보기]로 적립금·펀드 목록, [계약 목록]으로 카드 목록 복귀(보던 카드로 초점), 상단 계약 탭 삭제 / 고른 계약은 펀드변경과 공유, 계약종합현황 「펀드 수익률」에서 진입 시 해당 계약 상세 바로 표시</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>CT-05</t>
+          <t>CT-04</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -2318,7 +2322,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>연금지급내역 조회</t>
+          <t>휴면보험금 조회</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -2333,7 +2337,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>연금 수령자</t>
+          <t>계약자·수익자</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -2343,22 +2347,22 @@
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>지급일, 지급금액, 원천징수 세액, 실수령액</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
-        <is>
-          <t>조회기간</t>
-        </is>
-      </c>
-      <c r="K23" s="15" t="inlineStr">
+          <t>휴면보험금 목록, 금액, 발생일</t>
+        </is>
+      </c>
+      <c r="J23" s="15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>미수령보험금 신청 연결</t>
+        </is>
+      </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>지급</t>
+          <t>보전</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr">
@@ -2366,9 +2370,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N23" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
+      <c r="N23" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
         </is>
       </c>
       <c r="O23" s="10" t="n"/>
@@ -2376,7 +2380,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>CT-06</t>
+          <t>CT-05</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -2389,9 +2393,9 @@
           <t>보험계약조회</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>원천징수내역 조회</t>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>연금지급내역 조회</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -2406,7 +2410,7 @@
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>계약자·수익자</t>
+          <t>연금 수령자</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
@@ -2416,7 +2420,7 @@
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>지급 건별 원천징수 내역(이자소득·연금소득·기타소득 등)</t>
+          <t>지급일, 지급금액, 원천징수 세액, 실수령액</t>
         </is>
       </c>
       <c r="J24" s="13" t="inlineStr">
@@ -2434,9 +2438,9 @@
           <t>지급</t>
         </is>
       </c>
-      <c r="M24" s="11" t="inlineStr">
-        <is>
-          <t>소득세법</t>
+      <c r="M24" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="16" t="inlineStr">
@@ -2449,7 +2453,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>CT-07</t>
+          <t>CT-06</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -2464,7 +2468,7 @@
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>미래예상연금액 조회</t>
+          <t>원천징수내역 조회</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -2479,7 +2483,7 @@
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>연금 계약자</t>
+          <t>계약자·수익자</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -2489,12 +2493,12 @@
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
-          <t>연금개시일, 예상 연금액(연금유형별)</t>
+          <t>지급 건별 원천징수 내역(이자소득·연금소득·기타소득 등)</t>
         </is>
       </c>
       <c r="J25" s="13" t="inlineStr">
         <is>
-          <t>연금개시나이, 적용이율, 연금유형</t>
+          <t>조회기간</t>
         </is>
       </c>
       <c r="K25" s="15" t="inlineStr">
@@ -2504,17 +2508,17 @@
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>보전</t>
+          <t>지급</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>예시금액이며 확정 아님</t>
-        </is>
-      </c>
-      <c r="N25" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
+          <t>소득세법</t>
+        </is>
+      </c>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
       <c r="O25" s="10" t="n"/>
@@ -2522,7 +2526,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>CT-08</t>
+          <t>CT-07</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -2535,9 +2539,9 @@
           <t>보험계약조회</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>거래내역조회</t>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>미래예상연금액 조회</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -2552,7 +2556,7 @@
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>연금 계약자</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -2562,12 +2566,12 @@
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>거래일, 거래구분(납입·지급·대출·상환), 금액, 계좌, 채널</t>
+          <t>연금개시일, 예상 연금액(연금유형별)</t>
         </is>
       </c>
       <c r="J26" s="13" t="inlineStr">
         <is>
-          <t>조회기간·거래구분</t>
+          <t>연금개시나이, 적용이율, 연금유형</t>
         </is>
       </c>
       <c r="K26" s="15" t="inlineStr">
@@ -2577,12 +2581,12 @@
       </c>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>수금</t>
-        </is>
-      </c>
-      <c r="M26" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>보전</t>
+        </is>
+      </c>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>예시금액이며 확정 아님</t>
         </is>
       </c>
       <c r="N26" s="14" t="inlineStr">
@@ -2595,7 +2599,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>CT-09</t>
+          <t>CT-08</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -2610,7 +2614,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>전자서명계약서류 조회</t>
+          <t>거래내역조회</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -2635,22 +2639,22 @@
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
-          <t>전자서명 청약서, 상품설명서, 약관, 서명일시</t>
+          <t>거래일, 거래구분(납입·지급·대출·상환), 금액, 계좌, 채널</t>
         </is>
       </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>계약 선택</t>
+          <t>조회기간·거래구분</t>
         </is>
       </c>
       <c r="K27" s="15" t="inlineStr">
         <is>
-          <t>PDF 다운로드</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
-          <t>보전</t>
+          <t>수금</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
@@ -2658,9 +2662,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N27" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
+      <c r="N27" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
         </is>
       </c>
       <c r="O27" s="10" t="n"/>
@@ -2668,7 +2672,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>PY-01</t>
+          <t>CT-09</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -2678,27 +2682,27 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>보험금청구/신청</t>
+          <t>보험계약조회</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>보험금 청구</t>
+          <t>전자서명계약서류 조회</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>신청</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T2 목록+상세</t>
         </is>
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>계약자·피보험자·수익자</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -2708,44 +2712,40 @@
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>청구 가능 계약(타인 피보험자 계약 포함)·피보험자, 필요서류 안내</t>
+          <t>전자서명 청약서, 상품설명서, 약관, 서명일시</t>
         </is>
       </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>사고유형, 청구내용, 사고일·초진일, 수령계좌, 증빙 이미지 / 피보험자(선택한 계약의 피보험자로 미리 선택)</t>
-        </is>
-      </c>
-      <c r="K28" s="13" t="inlineStr">
-        <is>
-          <t>접수번호, 알림톡</t>
-        </is>
-      </c>
-      <c r="L28" s="12" t="inlineStr">
-        <is>
-          <t>사고</t>
-        </is>
-      </c>
-      <c r="M28" s="11" t="inlineStr">
-        <is>
-          <t>개인(신용)·민감정보 동의, 보험사기 경고</t>
-        </is>
-      </c>
-      <c r="N28" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O28" s="11" t="inlineStr">
-        <is>
-          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내</t>
-        </is>
-      </c>
+          <t>계약 선택</t>
+        </is>
+      </c>
+      <c r="K28" s="15" t="inlineStr">
+        <is>
+          <t>PDF 다운로드</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>보전</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="O28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>PY-02</t>
+          <t>PY-01</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -2760,22 +2760,22 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>보험금 청구 조회/서류추가</t>
+          <t>보험금 청구</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>신청</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>T2 목록+상세</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>청구인</t>
+          <t>계약자·피보험자·수익자</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>접수일, 진행단계, 지급결정액, 보완서류 요청 내역</t>
+          <t>청구 가능 계약(타인 피보험자 계약 포함)·피보험자, 필요서류 안내</t>
         </is>
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>보완서류 이미지(1장 이상 필수)</t>
+          <t>사고유형, 청구내용, 사고일·초진일, 수령계좌, 증빙 이미지 / 피보험자(선택한 계약의 피보험자로 미리 선택)</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>서류 제출 완료 알림</t>
+          <t>접수번호, 알림톡</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
@@ -2805,24 +2805,24 @@
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>부지급 시 사유·재심사 안내</t>
-        </is>
-      </c>
-      <c r="N29" s="17" t="inlineStr">
+          <t>개인(신용)·민감정보 동의, 보험사기 경고</t>
+        </is>
+      </c>
+      <c r="N29" s="14" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="O29" s="10" t="inlineStr">
-        <is>
-          <t>v3.7: 선택한 청구 건에 제출 반영(진행단계 → 처리중), 보완서류 미첨부 시 오류 안내 후 제출 불가</t>
+      <c r="O29" s="11" t="inlineStr">
+        <is>
+          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>PY-03</t>
+          <t>PY-02</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>보험금 찾기</t>
+          <t>보험금 청구 조회/서류추가</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>계약자·수익자</t>
+          <t>청구인</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -2862,40 +2862,44 @@
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>수령 가능 보험금(휴면·미수령·만기·분할·배당) 통합 목록</t>
-        </is>
-      </c>
-      <c r="J30" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>접수일, 진행단계, 지급결정액, 보완서류 요청 내역</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>보완서류 이미지(1장 이상 필수)</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>유형별 신청 화면 연결</t>
+          <t>서류 제출 완료 알림</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>보전</t>
-        </is>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N30" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O30" s="11" t="n"/>
+          <t>사고</t>
+        </is>
+      </c>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>부지급 시 사유·재심사 안내</t>
+        </is>
+      </c>
+      <c r="N30" s="17" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O30" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 선택한 청구 건에 제출 반영(진행단계 → 처리중), 보완서류 미첨부 시 오류 안내 후 제출 불가</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>PY-04</t>
+          <t>PY-03</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -2910,65 +2914,65 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>분할/만기보험금 신청</t>
+          <t>보험금 찾기</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>지급</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T2 목록+상세</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>수익자</t>
+          <t>계약자·수익자</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>발생 지급금, 공제액, 실지급액</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
-        <is>
-          <t>지급 대상, 계좌</t>
+          <t>수령 가능 보험금(휴면·미수령·만기·분할·배당) 통합 목록</t>
+        </is>
+      </c>
+      <c r="J31" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>지급 완료 안내</t>
-        </is>
-      </c>
-      <c r="L31" s="9" t="inlineStr">
-        <is>
-          <t>지급</t>
-        </is>
-      </c>
-      <c r="M31" s="11" t="inlineStr">
-        <is>
-          <t>세금 원천징수</t>
-        </is>
-      </c>
-      <c r="N31" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O31" s="10" t="n"/>
+          <t>유형별 신청 화면 연결</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>보전</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="O31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>PY-05</t>
+          <t>PY-04</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2983,7 +2987,7 @@
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>중도인출 신청</t>
+          <t>분할/만기보험금 신청</t>
         </is>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2998,7 +3002,7 @@
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>유니버설·변액 계약자</t>
+          <t>수익자</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -3008,12 +3012,12 @@
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>인출 가능금액, 연간 인출 횟수, 공제액</t>
+          <t>발생 지급금, 공제액, 실지급액</t>
         </is>
       </c>
       <c r="J32" s="13" t="inlineStr">
         <is>
-          <t>인출금액, 계좌</t>
+          <t>지급 대상, 계좌</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
@@ -3028,7 +3032,7 @@
       </c>
       <c r="M32" s="11" t="inlineStr">
         <is>
-          <t>인출 시 보장·환급금 감소 고지</t>
+          <t>세금 원천징수</t>
         </is>
       </c>
       <c r="N32" s="14" t="inlineStr">
@@ -3041,7 +3045,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>PY-06</t>
+          <t>PY-05</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -3056,42 +3060,42 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>지급신청현황 조회/취소</t>
+          <t>중도인출 신청</t>
         </is>
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>지급</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>T2 목록+상세</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>신청인</t>
+          <t>유니버설·변액 계약자</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>신청일, 지급종류, 금액, 처리상태</t>
+          <t>인출 가능금액, 연간 인출 횟수, 공제액</t>
         </is>
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>취소 대상</t>
+          <t>인출금액, 계좌</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>취소 완료 안내</t>
+          <t>지급 완료 안내</t>
         </is>
       </c>
       <c r="L33" s="9" t="inlineStr">
@@ -3101,12 +3105,12 @@
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>처리 전 건만 취소</t>
-        </is>
-      </c>
-      <c r="N33" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
+          <t>인출 시 보장·환급금 감소 고지</t>
+        </is>
+      </c>
+      <c r="N33" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
         </is>
       </c>
       <c r="O33" s="10" t="n"/>
@@ -3114,7 +3118,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>PY-07</t>
+          <t>PY-06</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -3129,55 +3133,55 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>미수령보험금 신청</t>
+          <t>지급신청현황 조회/취소</t>
         </is>
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
+          <t>조회</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>T2 목록+상세</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>신청인</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>A1 인증서</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>신청일, 지급종류, 금액, 처리상태</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
+        <is>
+          <t>취소 대상</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>취소 완료 안내</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
           <t>지급</t>
         </is>
       </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>T3 단계형 신청</t>
-        </is>
-      </c>
-      <c r="G34" s="11" t="inlineStr">
-        <is>
-          <t>수익자</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>A1 인증서+추가인증</t>
-        </is>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>미수령·휴면 보험금 목록, 금액</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr">
-        <is>
-          <t>지급 대상, 계좌</t>
-        </is>
-      </c>
-      <c r="K34" s="13" t="inlineStr">
-        <is>
-          <t>지급 완료 안내</t>
-        </is>
-      </c>
-      <c r="L34" s="9" t="inlineStr">
-        <is>
-          <t>지급</t>
-        </is>
-      </c>
-      <c r="M34" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N34" s="17" t="inlineStr">
+      <c r="M34" s="11" t="inlineStr">
+        <is>
+          <t>처리 전 건만 취소</t>
+        </is>
+      </c>
+      <c r="N34" s="16" t="inlineStr">
         <is>
           <t>없음</t>
         </is>
@@ -3187,7 +3191,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>PY-08</t>
+          <t>PY-07</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -3202,17 +3206,17 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>자동송금 신청/해지</t>
+          <t>미수령보험금 신청</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>지급</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>T4 단일폼 변경</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -3227,17 +3231,17 @@
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
-          <t>자동송금 대상 지급금(분할·연금 등), 현재 등록 계좌</t>
+          <t>미수령·휴면 보험금 목록, 금액</t>
         </is>
       </c>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>계좌, 신청·해지</t>
+          <t>지급 대상, 계좌</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 알림</t>
+          <t>지급 완료 안내</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
@@ -3245,14 +3249,14 @@
           <t>지급</t>
         </is>
       </c>
-      <c r="M35" s="11" t="inlineStr">
-        <is>
-          <t>본인 명의 계좌</t>
-        </is>
-      </c>
-      <c r="N35" s="16" t="inlineStr">
-        <is>
-          <t>있음</t>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="17" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
       <c r="O35" s="10" t="n"/>
@@ -3260,7 +3264,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>PY-09</t>
+          <t>PY-08</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -3275,55 +3279,55 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>연금 지급 신청</t>
+          <t>자동송금 신청/해지</t>
         </is>
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>T4 단일폼 변경</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>수익자</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>A1 인증서+추가인증</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>자동송금 대상 지급금(분할·연금 등), 현재 등록 계좌</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr">
+        <is>
+          <t>계좌, 신청·해지</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>변경 완료 알림</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
           <t>지급</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>T3 단계형 신청</t>
-        </is>
-      </c>
-      <c r="G36" s="11" t="inlineStr">
-        <is>
-          <t>연금 수령자</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>A1 인증서+추가인증</t>
-        </is>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>연금 지급 예정액, 지급주기</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
-        <is>
-          <t>수령계좌, 확인</t>
-        </is>
-      </c>
-      <c r="K36" s="13" t="inlineStr">
-        <is>
-          <t>신청 완료 안내</t>
-        </is>
-      </c>
-      <c r="L36" s="9" t="inlineStr">
-        <is>
-          <t>지급</t>
-        </is>
-      </c>
       <c r="M36" s="11" t="inlineStr">
         <is>
-          <t>연금소득 과세 안내</t>
-        </is>
-      </c>
-      <c r="N36" s="17" t="inlineStr">
+          <t>본인 명의 계좌</t>
+        </is>
+      </c>
+      <c r="N36" s="16" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
@@ -3333,7 +3337,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>CH-11</t>
+          <t>PY-09</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -3348,12 +3352,12 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>연금전환 사전신청</t>
+          <t>연금 지급 신청</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>신청</t>
+          <t>지급</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
@@ -3363,54 +3367,50 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>계약자(종신보험)</t>
+          <t>연금 수령자</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>전환 가능 종신보험(적립금), 전환 시점 예상 적립금·연금액(예시)</t>
+          <t>연금 지급 예정액, 지급주기</t>
         </is>
       </c>
       <c r="J37" s="13" t="inlineStr">
         <is>
-          <t>대상 계약, 연금 전환 나이, 연금 유형, 지급 주기, 연금 받을 계좌</t>
+          <t>수령계좌, 확인</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>사전신청 접수·전환 예정일 30일 전 알림톡 안내</t>
+          <t>신청 완료 안내</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>보전</t>
-        </is>
-      </c>
-      <c r="M37" s="10" t="inlineStr">
-        <is>
-          <t>사망보장 소멸·감소 안내</t>
-        </is>
-      </c>
-      <c r="N37" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O37" s="10" t="inlineStr">
-        <is>
-          <t>v3.7 신규: 전환 예정일 전까지 변경·취소 가능 / v3.7: 2Depth 「보험계약관리」→「보험금청구/신청」 이동(연금 지급 신청 다음), 메뉴ID 유지</t>
-        </is>
-      </c>
+          <t>지급</t>
+        </is>
+      </c>
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t>연금소득 과세 안내</t>
+        </is>
+      </c>
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>PM-01</t>
+          <t>CH-11</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -3420,17 +3420,17 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>보험료납입/자동이체</t>
+          <t>보험금청구/신청</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>보험료 납입 관리</t>
+          <t>연금전환 사전신청</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>입금</t>
+          <t>신청</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>계약자(종신보험)</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
@@ -3450,40 +3450,44 @@
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>납입 대상 회차, 미납·연체 여부, 납입금액, 선납 할인</t>
-        </is>
-      </c>
-      <c r="J38" s="45" t="inlineStr">
-        <is>
-          <t>계약 선택, 납입 회차, 납입방법(계좌출금·가상계좌) / 납입 방법이 가상계좌면 발급 은행 선택(iM뱅크·농협), 내 계좌 출금이면 출금 계좌 선택</t>
-        </is>
-      </c>
-      <c r="K38" s="32" t="inlineStr">
-        <is>
-          <t>납입 완료 안내 / 가상계좌: 인증 후 「가상계좌 정보」(은행명·가상계좌번호(복사 버튼)·예금주명 「iM라이프」) + 이용안내(유효시간 내 입금, 입금 유효기간 신청일 오후 6시까지, 미입금 시 가상계좌 자동 폐기)</t>
+          <t>전환 가능 종신보험(적립금), 전환 시점 예상 적립금·연금액(예시)</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
+        <is>
+          <t>대상 계약, 연금 전환 나이, 연금 유형, 지급 주기, 연금 받을 계좌</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>사전신청 접수·전환 예정일 30일 전 알림톡 안내</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>수금</t>
+          <t>보전</t>
         </is>
       </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N38" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O38" s="10" t="n"/>
+          <t>사망보장 소멸·감소 안내</t>
+        </is>
+      </c>
+      <c r="N38" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="O38" s="10" t="inlineStr">
+        <is>
+          <t>v3.7 신규: 전환 예정일 전까지 변경·취소 가능 / v3.7: 2Depth 「보험계약관리」→「보험금청구/신청」 이동(연금 지급 신청 다음), 메뉴ID 유지</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>PM-02</t>
+          <t>PM-01</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -3498,17 +3502,17 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>보험료 자동이체 관리</t>
+          <t>보험료 납입 관리</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>입금</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>T4 단일폼 변경</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -3518,22 +3522,22 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>현재 이체 은행·계좌·이체일</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
-        <is>
-          <t>은행, 계좌, 이체일</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>변경 완료 알림</t>
+          <t>납입 대상 회차, 미납·연체 여부, 납입금액, 선납 할인</t>
+        </is>
+      </c>
+      <c r="J39" s="45" t="inlineStr">
+        <is>
+          <t>계약 선택, 납입 회차, 납입방법(계좌출금·가상계좌) / 납입 방법이 가상계좌면 발급 은행 선택(iM뱅크·농협), 내 계좌 출금이면 출금 계좌 선택</t>
+        </is>
+      </c>
+      <c r="K39" s="32" t="inlineStr">
+        <is>
+          <t>납입 완료 안내 / 가상계좌: 인증 후 「가상계좌 정보」(은행명·가상계좌번호(복사 버튼)·예금주명 「iM라이프」) + 이용안내(유효시간 내 입금, 입금 유효기간 신청일 오후 6시까지, 미입금 시 가상계좌 자동 폐기)</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
@@ -3541,9 +3545,9 @@
           <t>수금</t>
         </is>
       </c>
-      <c r="M39" s="11" t="inlineStr">
-        <is>
-          <t>출금 동의(전자서명)</t>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="14" t="inlineStr">
@@ -3551,12 +3555,16 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O39" s="10" t="n"/>
+      <c r="O39" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 출금 계좌 「다른 본인 계좌 등록」 선택 시 계좌 등록 레이어팝업(CM-09) — 계좌 확인(은행 조회) 후 등록, 등록한 계좌가 출금 계좌로 선택</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>PM-03</t>
+          <t>PM-02</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -3571,7 +3579,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>보험료 자동대출납입 신청/취소</t>
+          <t>보험료 자동이체 관리</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -3591,22 +3599,22 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>신청 여부, 대출 가능금액, 적용이율</t>
+          <t>현재 이체 은행·계좌·이체일</t>
         </is>
       </c>
       <c r="J40" s="13" t="inlineStr">
         <is>
-          <t>신청·취소</t>
+          <t>은행, 계좌, 이체일</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 안내</t>
+          <t>변경 완료 알림</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
@@ -3616,12 +3624,12 @@
       </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
-          <t>대출 이자 발생 고지</t>
-        </is>
-      </c>
-      <c r="N40" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
+          <t>출금 동의(전자서명)</t>
+        </is>
+      </c>
+      <c r="N40" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
         </is>
       </c>
       <c r="O40" s="10" t="n"/>
@@ -3629,7 +3637,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>PM-04</t>
+          <t>PM-03</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -3644,22 +3652,22 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>유니버설 자유납입 관리</t>
+          <t>보험료 자동대출납입 신청/취소</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>입금</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T4 단일폼 변경</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>유니버설 계약자</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -3669,17 +3677,17 @@
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>추가납입 한도·잔여 한도, 납입 일시중지 가능 여부</t>
+          <t>신청 여부, 대출 가능금액, 적용이율</t>
         </is>
       </c>
       <c r="J41" s="13" t="inlineStr">
         <is>
-          <t>추가납입 금액, 일시중지 신청</t>
+          <t>신청·취소</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>처리 완료 안내</t>
+          <t>변경 완료 안내</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
@@ -3689,12 +3697,12 @@
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>납입중지 시 월대체보험료 차감 고지</t>
-        </is>
-      </c>
-      <c r="N41" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
+          <t>대출 이자 발생 고지</t>
+        </is>
+      </c>
+      <c r="N41" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
       <c r="O41" s="10" t="n"/>
@@ -3702,7 +3710,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>CH-10</t>
+          <t>PM-04</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -3712,17 +3720,17 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>보험계약관리</t>
-        </is>
-      </c>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>계약관계자변경</t>
+          <t>보험료납입/자동이체</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>유니버설 자유납입 관리</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>입금</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
@@ -3732,37 +3740,37 @@
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>계약자(피보험자 동의 필요)</t>
+          <t>유니버설 계약자</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>현재 수익자(만기·사망·기타)</t>
+          <t>추가납입 한도·잔여 한도, 납입 일시중지 가능 여부</t>
         </is>
       </c>
       <c r="J42" s="13" t="inlineStr">
         <is>
-          <t>변경 수익자 정보, 피보험자 동의</t>
+          <t>추가납입 금액, 일시중지 신청</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 안내</t>
+          <t>처리 완료 안내</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>보전</t>
+          <t>수금</t>
         </is>
       </c>
       <c r="M42" s="11" t="inlineStr">
         <is>
-          <t>사망수익자 변경 시 피보험자 동의(상법)</t>
+          <t>납입중지 시 월대체보험료 차감 고지</t>
         </is>
       </c>
       <c r="N42" s="14" t="inlineStr">
@@ -3775,7 +3783,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>CH-05</t>
+          <t>CH-10</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -3788,9 +3796,9 @@
           <t>보험계약관리</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>보험기간/연금개시연도 변경</t>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>계약관계자변경</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -3805,22 +3813,22 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>계약자(피보험자 동의 필요)</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
-          <t>연금 계약 카드(현재 연금개시 나이·일자, 납입 현황, 적립금), 변경 가능 범위(55~80세)</t>
+          <t>현재 수익자(만기·사망·기타)</t>
         </is>
       </c>
       <c r="J43" s="13" t="inlineStr">
         <is>
-          <t>대상 계약(카드 라디오 선택), 변경 후 연금개시 나이</t>
+          <t>변경 수익자 정보, 피보험자 동의</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -3833,26 +3841,22 @@
           <t>보전</t>
         </is>
       </c>
-      <c r="M43" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N43" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O43" s="10" t="inlineStr">
-        <is>
-          <t>선택 → 입력 → 인증 → 완료 (확인 단계 생략)</t>
-        </is>
-      </c>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>사망수익자 변경 시 피보험자 동의(상법)</t>
+        </is>
+      </c>
+      <c r="N43" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>CH-07</t>
+          <t>CH-05</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -3867,7 +3871,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>연금개시유형 선택/변경</t>
+          <t>보험기간/연금개시연도 변경</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -3882,7 +3886,7 @@
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>연금 계약자</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -3890,14 +3894,14 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I44" s="32" t="inlineStr">
-        <is>
-          <t>연금 계약(선택 단계), 선택 요약·월 환산 예상액·회당 예상 연금액(지급주기 반영, 예시)</t>
-        </is>
-      </c>
-      <c r="J44" s="32" t="inlineStr">
-        <is>
-          <t>연금유형, 개인형/부부형, 연금비율, 체증형태, 체증기간, 체증율, 확정기간, 보증기간, 지급주기, 조기집중형보장배수 (10개 선택조건)</t>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>연금 계약 카드(현재 연금개시 나이·일자, 납입 현황, 적립금), 변경 가능 범위(55~80세)</t>
+        </is>
+      </c>
+      <c r="J44" s="13" t="inlineStr">
+        <is>
+          <t>대상 계약(카드 라디오 선택), 변경 후 연금개시 나이</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -3910,26 +3914,26 @@
           <t>보전</t>
         </is>
       </c>
-      <c r="M44" s="33" t="inlineStr">
-        <is>
-          <t>개시 후 변경 제한 고지 / 예상 연금액은 예시(확정 아님)</t>
-        </is>
-      </c>
-      <c r="N44" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O44" s="34" t="inlineStr">
-        <is>
-          <t>v3.3: 연금유형별 고정값 규칙 적용(상세: 「선택조건_CH-07」 시트) · 고정 항목은 고정값만 표시·선택 불가 · 입력 영역 PC 2열/모바일 2열(긴 항목 1열) 촘촘한 버튼형 배치</t>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="O44" s="10" t="inlineStr">
+        <is>
+          <t>선택 → 입력 → 인증 → 완료 (확인 단계 생략)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>CH-01</t>
+          <t>CH-07</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -3944,7 +3948,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>변액보험 펀드변경/관리</t>
+          <t>연금개시유형 선택/변경</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -3954,12 +3958,12 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>T4 단일폼 변경</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>변액 계약자</t>
+          <t>연금 계약자</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
@@ -3969,27 +3973,27 @@
       </c>
       <c r="I45" s="32" t="inlineStr">
         <is>
-          <t>펀드별 위험등급·현재 비율·1년 수익률, 적립금·잔여 변경 횟수·투자성향, 최근 적합성진단일·투자 가능 범위, 변경 후 포트폴리오 위험등급(실시간), 변경 전후 비교(편입비율 막대·펀드별 증감·포트폴리오 위험등급·자동재배분·남은 변경 횟수)</t>
+          <t>연금 계약(선택 단계), 선택 요약·월 환산 예상액·회당 예상 연금액(지급주기 반영, 예시)</t>
         </is>
       </c>
       <c r="J45" s="32" t="inlineStr">
         <is>
-          <t>변경 펀드·비율(합계 100%), 자동재배분 / (필요 시) 적합성진단 5문항</t>
-        </is>
-      </c>
-      <c r="K45" s="32" t="inlineStr">
-        <is>
-          <t>변경 전후 비교 확인 후 인증 → 변경 접수·적용일 안내 / 진단 결과 불가 시 변경 불가·익일 재진행 안내</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>변액</t>
+          <t>연금유형, 개인형/부부형, 연금비율, 체증형태, 체증기간, 체증율, 확정기간, 보증기간, 지급주기, 조기집중형보장배수 (10개 선택조건)</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>변경 완료 안내</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>보전</t>
         </is>
       </c>
       <c r="M45" s="33" t="inlineStr">
         <is>
-          <t>적합성원칙(금융소비자보호법) · 투자위험 고지 · 진단 후 3년 유효 · 부적합 시 당일 재진단 불가</t>
+          <t>개시 후 변경 제한 고지 / 예상 연금액은 예시(확정 아님)</t>
         </is>
       </c>
       <c r="N45" s="14" t="inlineStr">
@@ -3999,14 +4003,14 @@
       </c>
       <c r="O45" s="34" t="inlineStr">
         <is>
-          <t>v3.4: 변경 후 비율 입력 → 다음 → 적합성진단 필요 판단(①진단 후 3년 경과 ②변경 후 편입비율 위험 &gt; 현재 투자성향) → (필요 시) 진단 → 변경 전후 비교 → 인증 → 완료 / 진단 불가 시 익일 재진행 안내 · 변경 내용 없으면 진행 불가 (상세: 「적합성진단_CH-01」 시트) / 변액 계약이 2건 이상이면 상단 계약 탭으로 선택(변액보험 조회·펀드변경 간 선택 유지, 계약카드 「펀드 수익률」에서 진입 시 해당 계약 선택)</t>
+          <t>v3.3: 연금유형별 고정값 규칙 적용(상세: 「선택조건_CH-07」 시트) · 고정 항목은 고정값만 표시·선택 불가 · 입력 영역 PC 2열/모바일 2열(긴 항목 1열) 촘촘한 버튼형 배치</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>CH-02</t>
+          <t>CH-01</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -4021,7 +4025,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>감액완납</t>
+          <t>변액보험 펀드변경/관리</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -4031,12 +4035,12 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T4 단일폼 변경</t>
         </is>
       </c>
       <c r="G46" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>변액 계약자</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -4044,42 +4048,46 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>감액완납 후 가입금액·보장, 이후 납입 면제</t>
-        </is>
-      </c>
-      <c r="J46" s="13" t="inlineStr">
-        <is>
-          <t>확인 동의</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>변경 완료 안내</t>
-        </is>
-      </c>
-      <c r="L46" s="9" t="inlineStr">
-        <is>
-          <t>보전</t>
-        </is>
-      </c>
-      <c r="M46" s="11" t="inlineStr">
-        <is>
-          <t>특약 소멸 고지</t>
-        </is>
-      </c>
-      <c r="N46" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O46" s="10" t="n"/>
+      <c r="I46" s="32" t="inlineStr">
+        <is>
+          <t>펀드별 위험등급·현재 비율·1년 수익률, 적립금·잔여 변경 횟수·투자성향, 최근 적합성진단일·투자 가능 범위, 변경 후 포트폴리오 위험등급(실시간), 변경 전후 비교(편입비율 막대·펀드별 증감·포트폴리오 위험등급·자동재배분·남은 변경 횟수)</t>
+        </is>
+      </c>
+      <c r="J46" s="32" t="inlineStr">
+        <is>
+          <t>변경 펀드·비율(합계 100%), 자동재배분 / (필요 시) 적합성진단 5문항</t>
+        </is>
+      </c>
+      <c r="K46" s="32" t="inlineStr">
+        <is>
+          <t>변경 전후 비교 확인 후 인증 → 변경 접수·적용일 안내 / 진단 결과 불가 시 변경 불가·익일 재진행 안내</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="inlineStr">
+        <is>
+          <t>변액</t>
+        </is>
+      </c>
+      <c r="M46" s="33" t="inlineStr">
+        <is>
+          <t>적합성원칙(금융소비자보호법) · 투자위험 고지 · 진단 후 3년 유효 · 부적합 시 당일 재진단 불가</t>
+        </is>
+      </c>
+      <c r="N46" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O46" s="34" t="inlineStr">
+        <is>
+          <t>v3.4: 변경 후 비율 입력 → 다음 → 적합성진단 필요 판단(①진단 후 3년 경과 ②변경 후 편입비율 위험 &gt; 현재 투자성향) → (필요 시) 진단 → 변경 전후 비교 → 인증 → 완료 / 진단 불가 시 익일 재진행 안내 · 변경 내용 없으면 진행 불가 (상세: 「적합성진단_CH-01」 시트) / 변액 계약이 2건 이상이면 상단 계약 탭으로 선택(변액보험 조회·펀드변경 간 선택 유지, 계약카드 「펀드 수익률」에서 진입 시 해당 계약 선택)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>CH-03</t>
+          <t>CH-02</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -4094,7 +4102,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>특약해지</t>
+          <t>감액완납</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -4119,12 +4127,12 @@
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
-          <t>특약 목록, 해지 시 환급금·변경 후 보험료</t>
+          <t>감액완납 후 가입금액·보장, 이후 납입 면제</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr">
         <is>
-          <t>해지 특약 선택</t>
+          <t>확인 동의</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -4139,7 +4147,7 @@
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>변경 전후 보장 비교 고지</t>
+          <t>특약 소멸 고지</t>
         </is>
       </c>
       <c r="N47" s="16" t="inlineStr">
@@ -4152,7 +4160,7 @@
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>CH-04</t>
+          <t>CH-03</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -4167,12 +4175,12 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>보험계약 해지</t>
+          <t>특약해지</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>지급</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
@@ -4182,42 +4190,42 @@
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
-          <t>계약자(=수익자)</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>예상 해지환급금, 대출 상계액, 실수령액, 해지 시 불이익, 유지 권유</t>
+          <t>특약 목록, 해지 시 환급금·변경 후 보험료</t>
         </is>
       </c>
       <c r="J48" s="13" t="inlineStr">
         <is>
-          <t>해지 사유, 계좌, 확인 동의</t>
+          <t>해지 특약 선택</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>해지 완료·환급금 입금</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr">
-        <is>
-          <t>지급</t>
+          <t>변경 완료 안내</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>보전</t>
         </is>
       </c>
       <c r="M48" s="11" t="inlineStr">
         <is>
-          <t>해지 불이익 설명·확인(금소법)</t>
-        </is>
-      </c>
-      <c r="N48" s="17" t="inlineStr">
-        <is>
-          <t>부분</t>
+          <t>변경 전후 보장 비교 고지</t>
+        </is>
+      </c>
+      <c r="N48" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
       <c r="O48" s="10" t="n"/>
@@ -4225,7 +4233,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>CH-09</t>
+          <t>CH-04</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -4238,59 +4246,59 @@
           <t>보험계약관리</t>
         </is>
       </c>
-      <c r="D49" s="18" t="inlineStr">
-        <is>
-          <t>대리청구인 지정/등록</t>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>보험계약 해지</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>지급</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>T4 단일폼 변경</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>계약자(피보험자=수익자 계약)</t>
+          <t>계약자(=수익자)</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
-          <t>현재 지정 여부</t>
+          <t>예상 해지환급금, 대출 상계액, 실수령액, 해지 시 불이익, 유지 권유</t>
         </is>
       </c>
       <c r="J49" s="13" t="inlineStr">
         <is>
-          <t>대리청구인 정보, 피보험자와의 관계</t>
+          <t>해지 사유, 계좌, 확인 동의</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>등록 완료 안내</t>
-        </is>
-      </c>
-      <c r="L49" s="9" t="inlineStr">
-        <is>
-          <t>보전</t>
+          <t>해지 완료·환급금 입금</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>지급</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>지정 가능 가족 범위</t>
-        </is>
-      </c>
-      <c r="N49" s="16" t="inlineStr">
-        <is>
-          <t>미확인</t>
+          <t>해지 불이익 설명·확인(금소법)</t>
+        </is>
+      </c>
+      <c r="N49" s="17" t="inlineStr">
+        <is>
+          <t>부분</t>
         </is>
       </c>
       <c r="O49" s="10" t="n"/>
@@ -4298,7 +4306,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>CH-08</t>
+          <t>CH-09</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -4311,9 +4319,9 @@
           <t>보험계약관리</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
-        <is>
-          <t>금융정보보호 신청/해제</t>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>대리청구인 지정/등록</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -4328,37 +4336,37 @@
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>계약자(피보험자=수익자 계약)</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>현재 보호 설정 여부</t>
+          <t>현재 지정 여부</t>
         </is>
       </c>
       <c r="J50" s="13" t="inlineStr">
         <is>
-          <t>신청·해제</t>
+          <t>대리청구인 정보, 피보험자와의 관계</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 알림</t>
+          <t>등록 완료 안내</t>
         </is>
       </c>
       <c r="L50" s="9" t="inlineStr">
         <is>
-          <t>고객</t>
-        </is>
-      </c>
-      <c r="M50" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>보전</t>
+        </is>
+      </c>
+      <c r="M50" s="11" t="inlineStr">
+        <is>
+          <t>지정 가능 가족 범위</t>
         </is>
       </c>
       <c r="N50" s="16" t="inlineStr">
@@ -4366,12 +4374,12 @@
           <t>미확인</t>
         </is>
       </c>
-      <c r="O50" s="11" t="n"/>
+      <c r="O50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>CH-06</t>
+          <t>CH-08</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -4386,17 +4394,17 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>청약철회</t>
+          <t>금융정보보호 신청/해제</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>지급</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T4 단일폼 변경</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4406,75 +4414,75 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>철회 가능 계약·기한, 반환 보험료</t>
+          <t>현재 보호 설정 여부</t>
         </is>
       </c>
       <c r="J51" s="13" t="inlineStr">
         <is>
-          <t>철회 사유, 환불계좌</t>
+          <t>신청·해제</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>철회 접수·환불 예정일</t>
+          <t>변경 완료 알림</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
-          <t>보전</t>
-        </is>
-      </c>
-      <c r="M51" s="11" t="inlineStr">
-        <is>
-          <t>청약철회권(금소법)</t>
+          <t>고객</t>
+        </is>
+      </c>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="16" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O51" s="10" t="n"/>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="O51" s="11" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>LN-01</t>
+          <t>CH-06</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>대출</t>
+          <t>보험</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>대출조회</t>
+          <t>보험계약관리</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>대출내역 조회</t>
+          <t>청약철회</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>지급</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>T2 목록+상세</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>차주</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
@@ -4484,30 +4492,30 @@
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
-          <t>대출종류, 대출일, 잔액, 적용이율, 이자 납입일, 미납이자</t>
-        </is>
-      </c>
-      <c r="J52" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>철회 가능 계약·기한, 반환 보험료</t>
+        </is>
+      </c>
+      <c r="J52" s="13" t="inlineStr">
+        <is>
+          <t>철회 사유, 환불계좌</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>상환·증명서 연결</t>
+          <t>철회 접수·환불 예정일</t>
         </is>
       </c>
       <c r="L52" s="9" t="inlineStr">
         <is>
-          <t>대출</t>
-        </is>
-      </c>
-      <c r="M52" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N52" s="14" t="inlineStr">
+          <t>보전</t>
+        </is>
+      </c>
+      <c r="M52" s="11" t="inlineStr">
+        <is>
+          <t>청약철회권(금소법)</t>
+        </is>
+      </c>
+      <c r="N52" s="16" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
@@ -4517,7 +4525,7 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>LN-02</t>
+          <t>LN-01</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -4527,47 +4535,47 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>보험계약대출</t>
+          <t>대출조회</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>보험계약대출 신청</t>
+          <t>대출내역 조회</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>지급</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T2 목록+상세</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>차주</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
-          <t>[선택] 전체 대출 가능금액, 대출 가능 계약 수, 대출 가능 계약 목록(이율 낮은 순 · 계약별 대출 가능금액·대출이율·기존 대출잔액), 계약별 배정 대출금액·예상 월 이자, 배정 합계 / [확인·완료] 대출 실행 계약 카드(계약별 대출금액·적용 이율·예상 월 이자), 평균 적용 이율, 예상 월 이자 합계</t>
-        </is>
-      </c>
-      <c r="J53" s="13" t="inlineStr">
-        <is>
-          <t>[선택] 대출 신청금액(10만원 이상 ~ 전체 대출 가능금액) / [입력] 입금계좌, 필수 동의 (대출 신청금액 입력 없음)</t>
+          <t>대출종류, 대출일, 잔액, 적용이율, 이자 납입일, 미납이자</t>
+        </is>
+      </c>
+      <c r="J53" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>대출 실행·입금 안내, 대출 실행 계약을 카드로 표시(이율·대출금액)</t>
+          <t>상환·증명서 연결</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
@@ -4575,9 +4583,9 @@
           <t>대출</t>
         </is>
       </c>
-      <c r="M53" s="11" t="inlineStr">
-        <is>
-          <t>대출 상품설명·약정 전자서명</t>
+      <c r="M53" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="14" t="inlineStr">
@@ -4585,16 +4593,12 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O53" s="10" t="inlineStr">
-        <is>
-          <t>v3.1: 신청금액이 대출 가능금액보다 적으면 대출이율이 낮은 계약부터 순서대로 배정(계약별 가능금액까지 채운 뒤 다음 계약)</t>
-        </is>
-      </c>
+      <c r="O53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>LN-03</t>
+          <t>LN-02</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -4609,17 +4613,17 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>보험계약대출 신청 현황 조회/취소</t>
+          <t>보험계약대출 신청</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>지급</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>T2 목록+상세</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
@@ -4629,22 +4633,22 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>신청일, 신청금액, 처리상태</t>
+          <t>[선택] 전체 대출 가능금액, 대출 가능 계약 수, 대출 가능 계약 목록(이율 낮은 순 · 계약별 대출 가능금액·대출이율·기존 대출잔액), 계약별 배정 대출금액·예상 월 이자, 배정 합계 / [확인·완료] 대출 실행 계약 카드(계약별 대출금액·적용 이율·예상 월 이자), 평균 적용 이율, 예상 월 이자 합계</t>
         </is>
       </c>
       <c r="J54" s="13" t="inlineStr">
         <is>
-          <t>취소 대상</t>
+          <t>[선택] 대출 신청금액(10만원 이상 ~ 전체 대출 가능금액) / [입력] 입금계좌, 필수 동의 (대출 신청금액 입력 없음)</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>취소 완료 안내</t>
+          <t>대출 실행·입금 안내, 대출 실행 계약을 카드로 표시(이율·대출금액)</t>
         </is>
       </c>
       <c r="L54" s="9" t="inlineStr">
@@ -4654,20 +4658,24 @@
       </c>
       <c r="M54" s="11" t="inlineStr">
         <is>
-          <t>대출계약 철회권(금소법)</t>
-        </is>
-      </c>
-      <c r="N54" s="16" t="inlineStr">
-        <is>
-          <t>미확인</t>
-        </is>
-      </c>
-      <c r="O54" s="10" t="n"/>
+          <t>대출 상품설명·약정 전자서명</t>
+        </is>
+      </c>
+      <c r="N54" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O54" s="10" t="inlineStr">
+        <is>
+          <t>v3.1: 신청금액이 대출 가능금액보다 적으면 대출이율이 낮은 계약부터 순서대로 배정(계약별 가능금액까지 채운 뒤 다음 계약)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>LN-04</t>
+          <t>LN-03</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -4682,22 +4690,22 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>보험계약대출 상환/이자납입</t>
+          <t>보험계약대출 신청 현황 조회/취소</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>입금</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T2 목록+상세</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
         <is>
-          <t>차주</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
@@ -4707,17 +4715,17 @@
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
-          <t>대출 잔액, 미납 이자, 상환 후 잔액</t>
+          <t>신청일, 신청금액, 처리상태</t>
         </is>
       </c>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>상환구분(전액·일부·이자), 금액, 출금계좌</t>
+          <t>취소 대상</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>상환 완료 안내</t>
+          <t>취소 완료 안내</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
@@ -4725,14 +4733,14 @@
           <t>대출</t>
         </is>
       </c>
-      <c r="M55" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N55" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
+      <c r="M55" s="11" t="inlineStr">
+        <is>
+          <t>대출계약 철회권(금소법)</t>
+        </is>
+      </c>
+      <c r="N55" s="16" t="inlineStr">
+        <is>
+          <t>미확인</t>
         </is>
       </c>
       <c r="O55" s="10" t="n"/>
@@ -4740,7 +4748,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>LN-05</t>
+          <t>LN-04</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -4755,17 +4763,17 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>보험계약대출 정액분할상환</t>
+          <t>보험계약대출 상환/이자납입</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>입금</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>T4 단일폼 변경</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G56" s="11" t="inlineStr">
@@ -4780,17 +4788,17 @@
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>분할상환 가능 대출, 월 상환액 예시</t>
+          <t>대출 잔액, 미납 이자, 상환 후 잔액</t>
         </is>
       </c>
       <c r="J56" s="13" t="inlineStr">
         <is>
-          <t>월 상환액·이체일·계좌</t>
+          <t>상환구분(전액·일부·이자), 금액, 출금계좌</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>신청 완료 안내</t>
+          <t>상환 완료 안내</t>
         </is>
       </c>
       <c r="L56" s="9" t="inlineStr">
@@ -4813,7 +4821,7 @@
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>LN-06</t>
+          <t>LN-05</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -4823,12 +4831,12 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>보험계약대출 관리</t>
-        </is>
-      </c>
-      <c r="D57" s="18" t="inlineStr">
-        <is>
-          <t>원리금 자동이체 신청/해지</t>
+          <t>보험계약대출</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>보험계약대출 정액분할상환</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -4848,22 +4856,22 @@
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
-          <t>현재 이자 이체 계좌·이체일</t>
+          <t>분할상환 가능 대출, 월 상환액 예시</t>
         </is>
       </c>
       <c r="J57" s="13" t="inlineStr">
         <is>
-          <t>계좌, 이체일, 신청·해지</t>
+          <t>월 상환액·이체일·계좌</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 알림</t>
+          <t>신청 완료 안내</t>
         </is>
       </c>
       <c r="L57" s="9" t="inlineStr">
@@ -4881,67 +4889,67 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O57" s="11" t="n"/>
+      <c r="O57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>CF-01</t>
+          <t>LN-06</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>증명서발급</t>
+          <t>대출</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>보험</t>
+          <t>보험계약대출 관리</t>
         </is>
       </c>
       <c r="D58" s="18" t="inlineStr">
         <is>
-          <t>소득/세액공제 납입증명서</t>
+          <t>원리금 자동이체 신청/해지</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>발급</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>T5 발급</t>
+          <t>T4 단일폼 변경</t>
         </is>
       </c>
       <c r="G58" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>차주</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
-          <t>대상 연도, 계약별 공제대상 납입액</t>
+          <t>현재 이자 이체 계좌·이체일</t>
         </is>
       </c>
       <c r="J58" s="13" t="inlineStr">
         <is>
-          <t>연도, 수신방법(출력·PDF·이메일·팩스)</t>
+          <t>계좌, 이체일, 신청·해지</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>즉시 발급</t>
+          <t>변경 완료 알림</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr">
         <is>
-          <t>수금</t>
+          <t>대출</t>
         </is>
       </c>
       <c r="M58" s="10" t="inlineStr">
@@ -4949,17 +4957,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N58" s="16" t="inlineStr">
+      <c r="N58" s="14" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="O58" s="10" t="n"/>
+      <c r="O58" s="11" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>CF-02</t>
+          <t>CF-01</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -4972,9 +4980,9 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>보험료납입증명서</t>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>소득/세액공제 납입증명서</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -4999,12 +5007,12 @@
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
-          <t>계약 목록, 납입기간별 납입액</t>
+          <t>대상 연도, 계약별 공제대상 납입액</t>
         </is>
       </c>
       <c r="J59" s="13" t="inlineStr">
         <is>
-          <t>계약, 기간, 용도, 수신방법</t>
+          <t>연도, 수신방법(출력·PDF·이메일·팩스)</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -5032,7 +5040,7 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>CF-03</t>
+          <t>CF-02</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -5047,7 +5055,7 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>보험증권재발급</t>
+          <t>보험료납입증명서</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -5072,12 +5080,12 @@
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>계약 목록</t>
+          <t>계약 목록, 납입기간별 납입액</t>
         </is>
       </c>
       <c r="J60" s="13" t="inlineStr">
         <is>
-          <t>계약, 수신방법</t>
+          <t>계약, 기간, 용도, 수신방법</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -5087,7 +5095,7 @@
       </c>
       <c r="L60" s="9" t="inlineStr">
         <is>
-          <t>보전</t>
+          <t>수금</t>
         </is>
       </c>
       <c r="M60" s="10" t="inlineStr">
@@ -5097,7 +5105,7 @@
       </c>
       <c r="N60" s="16" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="O60" s="10" t="n"/>
@@ -5105,7 +5113,7 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>CF-04</t>
+          <t>CF-03</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -5120,7 +5128,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>해지환급금증명서</t>
+          <t>보험증권재발급</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -5145,12 +5153,12 @@
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
-          <t>계약 목록, 기준일 해지환급금</t>
+          <t>계약 목록</t>
         </is>
       </c>
       <c r="J61" s="13" t="inlineStr">
         <is>
-          <t>계약, 기준일, 수신방법</t>
+          <t>계약, 수신방법</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -5158,9 +5166,9 @@
           <t>즉시 발급</t>
         </is>
       </c>
-      <c r="L61" s="12" t="inlineStr">
-        <is>
-          <t>지급</t>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>보전</t>
         </is>
       </c>
       <c r="M61" s="10" t="inlineStr">
@@ -5170,7 +5178,7 @@
       </c>
       <c r="N61" s="16" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="O61" s="10" t="n"/>
@@ -5178,7 +5186,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>CF-05</t>
+          <t>CF-04</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -5191,9 +5199,9 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="D62" s="19" t="inlineStr">
-        <is>
-          <t>사고보험금지급명세</t>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>해지환급금증명서</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -5216,14 +5224,14 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I62" s="15" t="inlineStr">
-        <is>
-          <t>청구사항 목록, 지급설명서</t>
-        </is>
-      </c>
-      <c r="J62" s="15" t="inlineStr">
-        <is>
-          <t>청구, 지급일, 수신방법</t>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>계약 목록, 기준일 해지환급금</t>
+        </is>
+      </c>
+      <c r="J62" s="13" t="inlineStr">
+        <is>
+          <t>계약, 기준일, 수신방법</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -5233,7 +5241,7 @@
       </c>
       <c r="L62" s="12" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>지급</t>
         </is>
       </c>
       <c r="M62" s="10" t="inlineStr">
@@ -5243,7 +5251,7 @@
       </c>
       <c r="N62" s="16" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="O62" s="10" t="n"/>
@@ -5251,7 +5259,7 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>CF-06</t>
+          <t>CF-05</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -5261,12 +5269,12 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>대출</t>
-        </is>
-      </c>
-      <c r="D63" s="18" t="inlineStr">
-        <is>
-          <t>보험계약대출 증명서</t>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>사고보험금지급명세</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -5281,7 +5289,7 @@
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>차주</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
@@ -5289,14 +5297,14 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>보험계약대출 목록, 잔액·거래내역</t>
+      <c r="I63" s="15" t="inlineStr">
+        <is>
+          <t>청구사항 목록, 지급설명서</t>
         </is>
       </c>
       <c r="J63" s="15" t="inlineStr">
         <is>
-          <t>기준일·기간, 수신방법</t>
+          <t>청구, 지급일, 수신방법</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -5304,9 +5312,9 @@
           <t>즉시 발급</t>
         </is>
       </c>
-      <c r="L63" s="9" t="inlineStr">
-        <is>
-          <t>대출</t>
+      <c r="L63" s="12" t="inlineStr">
+        <is>
+          <t>사고</t>
         </is>
       </c>
       <c r="M63" s="10" t="inlineStr">
@@ -5316,30 +5324,30 @@
       </c>
       <c r="N63" s="16" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O63" s="20" t="n"/>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="O63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>CS-01</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>서류·안내</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>제지급/신청서류</t>
-        </is>
-      </c>
-      <c r="D64" s="19" t="inlineStr">
-        <is>
-          <t>사고보험금 청구서류</t>
+          <t>CF-06</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>증명서발급</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>대출</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>보험계약대출 증명서</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -5354,22 +5362,22 @@
       </c>
       <c r="G64" s="11" t="inlineStr">
         <is>
-          <t>청구인</t>
+          <t>차주</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>A0 비로그인</t>
-        </is>
-      </c>
-      <c r="I64" s="15" t="inlineStr">
-        <is>
-          <t>사고보험금 청구서류 목록</t>
-        </is>
-      </c>
-      <c r="J64" s="21" t="inlineStr">
-        <is>
-          <t>청구서류 종류(출럭 PDF)</t>
+          <t>A1 인증서</t>
+        </is>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>보험계약대출 목록, 잔액·거래내역</t>
+        </is>
+      </c>
+      <c r="J64" s="15" t="inlineStr">
+        <is>
+          <t>기준일·기간, 수신방법</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -5377,9 +5385,9 @@
           <t>즉시 발급</t>
         </is>
       </c>
-      <c r="L64" s="12" t="inlineStr">
-        <is>
-          <t>사고</t>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>대출</t>
         </is>
       </c>
       <c r="M64" s="10" t="inlineStr">
@@ -5389,86 +5397,159 @@
       </c>
       <c r="N64" s="16" t="inlineStr">
         <is>
-          <t>미확인</t>
-        </is>
-      </c>
-      <c r="O64" s="11" t="n"/>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O64" s="20" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
+          <t>CS-01</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>서류·안내</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>제지급/신청서류</t>
+        </is>
+      </c>
+      <c r="D65" s="19" t="inlineStr">
+        <is>
+          <t>사고보험금 청구서류</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>발급</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>T5 발급</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>청구인</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="inlineStr">
+        <is>
+          <t>A0 비로그인</t>
+        </is>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
+        <is>
+          <t>사고보험금 청구서류 목록</t>
+        </is>
+      </c>
+      <c r="J65" s="21" t="inlineStr">
+        <is>
+          <t>청구서류 종류(출럭 PDF)</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>즉시 발급</t>
+        </is>
+      </c>
+      <c r="L65" s="12" t="inlineStr">
+        <is>
+          <t>사고</t>
+        </is>
+      </c>
+      <c r="M65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="16" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="O65" s="11" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
           <t>CS-02</t>
         </is>
       </c>
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>서류·안내</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>제지급/신청서류</t>
         </is>
       </c>
-      <c r="D65" s="19" t="inlineStr">
+      <c r="D66" s="19" t="inlineStr">
         <is>
           <t>제지급 서류</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>발급</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F66" s="10" t="inlineStr">
         <is>
           <t>T5 발급</t>
         </is>
       </c>
-      <c r="G65" s="11" t="inlineStr">
+      <c r="G66" s="11" t="inlineStr">
         <is>
           <t>청구인</t>
         </is>
       </c>
-      <c r="H65" s="12" t="inlineStr">
+      <c r="H66" s="12" t="inlineStr">
         <is>
           <t>A0 비로그인</t>
         </is>
       </c>
-      <c r="I65" s="15" t="inlineStr">
+      <c r="I66" s="15" t="inlineStr">
         <is>
           <t>제지급 서류 목록</t>
         </is>
       </c>
-      <c r="J65" s="21" t="inlineStr">
+      <c r="J66" s="21" t="inlineStr">
         <is>
           <t>청구서류 종류(출럭 PDF)</t>
         </is>
       </c>
-      <c r="K65" s="13" t="inlineStr">
+      <c r="K66" s="13" t="inlineStr">
         <is>
           <t>즉시 발급</t>
         </is>
       </c>
-      <c r="L65" s="12" t="inlineStr">
+      <c r="L66" s="12" t="inlineStr">
         <is>
           <t>지급</t>
         </is>
       </c>
-      <c r="M65" s="10" t="inlineStr">
+      <c r="M66" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N65" s="16" t="inlineStr">
+      <c r="N66" s="16" t="inlineStr">
         <is>
           <t>미확인</t>
         </is>
       </c>
-      <c r="O65" s="11" t="n"/>
+      <c r="O66" s="11" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O64"/>
+  <autoFilter ref="A4:O65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -5895,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7772,6 +7853,60 @@
       <c r="E71" s="11" t="inlineStr">
         <is>
           <t>CT-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>다른 본인 계좌 등록 레이어팝업: 계좌 확인(은행 예금주 조회) 후에만 등록, 계좌 선택칸이 있는 모든 화면 공통</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>CM-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>출금 계좌 「다른 본인 계좌 등록」 선택 시 계좌 등록 팝업 호출, 등록한 계좌를 출금 계좌로 선택</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>PM-01</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7907,6 +7907,33 @@
       <c r="E73" s="11" t="inlineStr">
         <is>
           <t>PM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>헤더·모바일 상단 로고를 「iM」 글자 원에서 iM 심볼(iM_symbol.ai, SVG)로 교체</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>공통 헤더</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
-          <t>메인 상단 [바로가기 추가] 버튼(모바일은 안내 문구와 한 줄·작은 버튼). 원클릭 설치는 운영 HTTPS+웹앱 매니페스트 필요 / v3.7: 바로가기 파일은 지금 보고 있는 사이버창구 주소를 연다(설정 주소는 알 수 없을 때만) / v3.7: 크롬·엣지가 .url 을 .download 로 바꿔 저장하므로 Windows 는 zip(압축 파일) 안에 .url 로 제공, Mac .webloc 은 확장자가 덧붙지 않게 저장</t>
+          <t>메인 상단 [바로가기 추가] 버튼(모바일은 안내 문구와 한 줄·작은 버튼). 원클릭 설치는 운영 HTTPS+웹앱 매니페스트 필요 / v3.7: 바로가기 파일은 지금 보고 있는 사이버창구 주소를 연다(설정 주소는 알 수 없을 때만) / v3.7: 크롬·엣지가 .url 을 .download 로 바꿔 저장하므로 Windows 는 zip(압축 파일) 안에 .url 로 제공, Mac .webloc 은 확장자가 덧붙지 않게 저장 / v3.7: 바탕화면·홈 화면·브라우저 탭 아이콘은 흰 바탕 iM 심볼, [바로가기 추가] 버튼은 글자만(아이콘 없음)</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7934,6 +7934,60 @@
       <c r="E74" s="11" t="inlineStr">
         <is>
           <t>공통 헤더</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>브라우저 탭·홈 화면 바로가기 아이콘을 iM 심볼(흰 바탕)로 교체</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>CM-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>메인 [바로가기 추가] 버튼의 「iM」 아이콘 제거(글자만)</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>CM-01</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O11" s="10" t="inlineStr">
         <is>
-          <t>메인 상단 [바로가기 추가] 버튼(모바일은 안내 문구와 한 줄·작은 버튼). 원클릭 설치는 운영 HTTPS+웹앱 매니페스트 필요 / v3.7: 바로가기 파일은 지금 보고 있는 사이버창구 주소를 연다(설정 주소는 알 수 없을 때만) / v3.7: 크롬·엣지가 .url 을 .download 로 바꿔 저장하므로 Windows 는 zip(압축 파일) 안에 .url 로 제공, Mac .webloc 은 확장자가 덧붙지 않게 저장 / v3.7: 바탕화면·홈 화면·브라우저 탭 아이콘은 흰 바탕 iM 심볼, [바로가기 추가] 버튼은 글자만(아이콘 없음)</t>
+          <t>메인 상단 [바로가기 추가] 버튼(모바일은 안내 문구와 한 줄·작은 버튼). 원클릭 설치는 운영 HTTPS+웹앱 매니페스트 필요 / v3.7: 바로가기 파일은 지금 보고 있는 사이버창구 주소를 연다(설정 주소는 알 수 없을 때만) / v3.7: 크롬·엣지가 .url 을 .download 로 바꿔 저장하므로 Windows 는 zip(압축 파일) 안에 .url 로 제공, Mac .webloc 은 확장자가 덧붙지 않게 저장 / v3.7: 바탕화면·홈 화면·브라우저 탭 아이콘은 흰 바탕 iM 심볼, [바로가기 추가] 버튼은 문구 앞에 iM 심볼</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7986,6 +7986,33 @@
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>CM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>메인 [바로가기 추가] 버튼: 문구 앞에 iM 심볼 표시(「iM」 글자 아이콘 대체)</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
         <is>
           <t>CM-01</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -2785,12 +2785,12 @@
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>청구 가능 계약(타인 피보험자 계약 포함)·피보험자, 필요서류 안내</t>
+          <t>보험금 청구사항 안내(청구 대상·이용 가능 시간·확인할 사항·기타 사항), 보험금 청구 및 지급 절차(6단계), 청구 종류(본인보험금 접수·자녀보험금 접수·수익자 청구), 필요서류 안내</t>
         </is>
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>사고유형, 청구내용, 사고일·초진일, 수령계좌, 증빙 이미지 / 피보험자(선택한 계약의 피보험자로 미리 선택)</t>
+          <t>청구 종류, 피보험자(청구 종류에 맞는 선택지), 사고유형, 청구내용, 사고일·초진일, 수령계좌, 증빙 이미지</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내</t>
+          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 및 지급 절차·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=자녀(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현)</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8015,6 +8015,33 @@
       <c r="E77" s="11" t="inlineStr">
         <is>
           <t>CM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>보험금 청구 첫 화면: 계약 선택 대신 청구사항 안내·청구 및 지급 절차·청구 종류(본인·자녀·수익자) 선택, 청구 종류에 맞는 피보험자 선택지</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>PY-01</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 및 지급 절차·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=자녀(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현)</t>
+          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 및 지급 절차·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=미성년 자녀만 가능(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현)</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8040,6 +8040,33 @@
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>PY-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>보험금 청구 「자녀보험금 접수」 안내 문구: 피보험자 자녀가 미성년자일 때에만 가능</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
         <is>
           <t>PY-01</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -2785,7 +2785,7 @@
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>보험금 청구사항 안내(청구 대상·이용 가능 시간·확인할 사항·기타 사항), 보험금 청구 및 지급 절차(6단계), 청구 종류(본인보험금 접수·자녀보험금 접수·수익자 청구), 필요서류 안내</t>
+          <t>보험금 청구사항 안내(청구 대상·이용 가능 시간·확인할 사항·기타 사항), 청구 종류(본인보험금 접수·자녀보험금 접수·수익자 청구), 필요서류 안내</t>
         </is>
       </c>
       <c r="J29" s="13" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 및 지급 절차·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=미성년 자녀만 가능(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현)</t>
+          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=미성년 자녀만 가능(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현)</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8067,6 +8067,33 @@
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>PY-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>보험금 청구 안내 단계에서 「보험금 청구 및 지급 절차」(6단계) 블록 삭제</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
         <is>
           <t>PY-01</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -2790,7 +2790,7 @@
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>청구 종류, 피보험자(청구 종류에 맞는 선택지), 사고유형, 청구내용, 사고일·초진일, 수령계좌, 증빙 이미지</t>
+          <t>청구 종류, 피보험자(청구 종류에 맞는 선택지), 사고유형(질병·재해·기타), 청구내용, 사고일, 사고장소(초진병원, 필수), 사고 발생경위(육하원칙, 선택), 초진일, 수령계좌, 증빙 이미지</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=미성년 자녀만 가능(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현)</t>
+          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=미성년 자녀만 가능(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현) / v3.7: 사고 유형 질병·재해·기타로 변경, 사고일 다음에 사고장소(초진병원) 필수 입력과 사고(발생경위) 여러 줄 입력(안내: 육하원칙, 예: 오늘 계단을 급하게 내려가다 발목을 접지름) 추가, 기존 병원명(선택) 항목은 사고장소(초진병원)로 대체</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8094,6 +8094,33 @@
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>PY-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>보험금 청구 입력: 사고 유형(질병·재해·기타), 사고장소(초진병원) 필수·사고 발생경위 추가, 병원명 항목 대체</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
         <is>
           <t>PY-01</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -1700,7 +1700,7 @@
       </c>
       <c r="O14" s="10" t="inlineStr">
         <is>
-          <t>변경한 연락처는 보유 계약 전체에 일괄 적용 (적용할 계약 선택 항목 없음)</t>
+          <t>변경한 연락처는 보유 계약 전체에 일괄 적용 (적용할 계약 선택 항목 없음) / v3.7: 화면 진입 시 「개인정보 유출 주의」 팝업(다른사람의 요청으로 개인정보를 변경하나요?) — 예: 메인으로 이동 / 아니요: 변경 화면 이용. 닫기(X)·Esc 없음, 뒤로 이동·로그인 후 진입 때도 다시 확인</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8123,6 +8123,33 @@
       <c r="E81" s="11" t="inlineStr">
         <is>
           <t>PY-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>개인정보변경 진입 시 「개인정보 유출 주의」 확인 팝업: 예 → 메인, 아니요일 때만 변경 가능</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>MY-01</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -1670,12 +1670,12 @@
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>현재 주소(자택·직장), 휴대폰·자택·직장 전화, 이메일</t>
+          <t>연락처(휴대폰번호·이메일), 자택정보(자택주소·자택전화), 직장정보(직장주소·직장전화) — 현재 등록 정보는 가려서 표시(휴대폰 010-****-5678, 이메일 아이디 앞 2자리, 상세주소 ****, 전화 가운데 ****)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t>자택/회사 주소(우편번호 검색), 전화번호, 휴대폰, 이메일</t>
+          <t>휴대폰번호(휴대폰인증), 이메일 아이디·도메인(중복확인), 자택/직장 주소(주소 검색 + 상세주소), 자택/직장 전화(세 칸) — 입력한 항목만 변경, 비우면 현재 정보 유지</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="O14" s="10" t="inlineStr">
         <is>
-          <t>변경한 연락처는 보유 계약 전체에 일괄 적용 (적용할 계약 선택 항목 없음) / v3.7: 화면 진입 시 「개인정보 유출 주의」 팝업(다른사람의 요청으로 개인정보를 변경하나요?) — 예: 메인으로 이동 / 아니요: 변경 화면 이용. 닫기(X)·Esc 없음, 뒤로 이동·로그인 후 진입 때도 다시 확인</t>
+          <t>변경한 연락처는 보유 계약 전체에 일괄 적용 (적용할 계약 선택 항목 없음) / v3.7: 화면 진입 시 「개인정보 유출 주의」 팝업(다른사람의 요청으로 개인정보를 변경하나요?) — 예: 메인으로 이동 / 아니요: 변경 화면 이용. 닫기(X)·Esc 없음, 뒤로 이동·로그인 후 진입 때도 다시 확인 / v3.7: 화면을 연락처·자택정보·직장정보 3구역으로 재구성, 필수 표시(휴대폰번호·이메일·자택주소), 자택·직장 중 1개 이상 주소 입력 안내. 휴대폰번호 변경은 본인명의 휴대폰 인증 후, 이메일 변경은 중복확인 후, 검색으로 바꾼 주소는 상세주소 필수, 바꾼 내용이 없으면 진행 불가</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8148,6 +8148,33 @@
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>MY-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>개인정보변경 화면 재구성(연락처·자택정보·직장정보), 현재 정보 가림 표시, 휴대폰인증·이메일 중복확인·주소 검색</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
         <is>
           <t>MY-01</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -1700,7 +1700,7 @@
       </c>
       <c r="O14" s="10" t="inlineStr">
         <is>
-          <t>변경한 연락처는 보유 계약 전체에 일괄 적용 (적용할 계약 선택 항목 없음) / v3.7: 화면 진입 시 「개인정보 유출 주의」 팝업(다른사람의 요청으로 개인정보를 변경하나요?) — 예: 메인으로 이동 / 아니요: 변경 화면 이용. 닫기(X)·Esc 없음, 뒤로 이동·로그인 후 진입 때도 다시 확인 / v3.7: 화면을 연락처·자택정보·직장정보 3구역으로 재구성, 필수 표시(휴대폰번호·이메일·자택주소), 자택·직장 중 1개 이상 주소 입력 안내. 휴대폰번호 변경은 본인명의 휴대폰 인증 후, 이메일 변경은 중복확인 후, 검색으로 바꾼 주소는 상세주소 필수, 바꾼 내용이 없으면 진행 불가</t>
+          <t>변경한 연락처는 보유 계약 전체에 일괄 적용 (적용할 계약 선택 항목 없음) / v3.7: 화면 진입 시 「개인정보 유출 주의」 팝업(다른사람의 요청으로 개인정보를 변경하나요?) — 예: 메인으로 이동 / 아니요: 변경 화면 이용. 닫기(X)·Esc 없음, 뒤로 이동·로그인 후 진입 때도 다시 확인 / v3.7: 화면을 연락처·자택정보·직장정보 3구역으로 재구성, 필수 표시(휴대폰번호·이메일·자택주소), 자택·직장 중 1개 이상 주소 입력 안내. 휴대폰번호 변경은 본인명의 휴대폰 인증 후, 이메일 변경은 중복확인 후, 검색으로 바꾼 주소는 상세주소 필수, 바꾼 내용이 없으면 진행 불가 / v3.7: 이메일 입력 순서 = 아이디 + @ + 도메인 칸 + 도메인 선택(선택·현재 도메인·주요 도메인·직접 입력). 도메인을 고르면 도메인 칸에 채움(입력 불가), 「직접 입력」이면 도메인 칸을 비우고 입력 가능(비우면 「이메일 도메인을 입력해 주세요」)</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8175,6 +8175,33 @@
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>MY-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>개인정보변경 이메일: 아이디 @ 도메인 칸 + 도메인 선택, 「직접 입력」 선택 시 도메인 칸 입력 가능</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
         <is>
           <t>MY-01</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8202,6 +8202,33 @@
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>MY-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>「개인정보 유출 주의」 팝업: 내용 가운데 정렬, 팝업·버튼 크기 축소</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
         <is>
           <t>MY-01</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -1777,7 +1777,7 @@
       </c>
       <c r="O15" s="34" t="inlineStr">
         <is>
-          <t>v3.1: 우편을 자택·직장으로 분리, 선택 안내장에만 「받지 않음」 제공 / 전자적방법 수신동의 문구: 「보험서비스에 관련된 안내장을 전자적방법(이메일, 모바일 등)으로 수신하는 것에 동의 합니다.」 — 이메일 항목 다음 배치 / 연동: ① 모바일·이메일 선택 시 수신동의 자동 체크 ② 수신동의 해제 시 확인 레이어팝업(우측 상단 X 닫기, 하단 [아니오][예]) 「전자적방법 수신동의 체크 해제 시 안내장별 수신 방법을 우편으로 선택하셔야 합니다. 해제하시겠습니까?」 → 예: 모바일·이메일 수신 안내장을 우편(자택)으로 변경 후 해제 / 아니오·X·Esc: 팝업만 닫고 동의 유지</t>
+          <t>v3.1: 우편을 자택·직장으로 분리, 선택 안내장에만 「받지 않음」 제공 / 전자적방법 수신동의 문구: 「보험서비스에 관련된 안내장을 전자적방법(이메일, 모바일 등)으로 수신하는 것에 동의 합니다.」 — 이메일 항목 다음 배치 / 연동: ① 모바일·이메일 선택 시 수신동의 자동 체크 ② 수신동의 해제 시 확인 레이어팝업(우측 상단 X 닫기, 하단 [아니오][예]) 「전자적방법 수신동의 체크 해제 시 안내장별 수신 방법을 우편으로 선택하셔야 합니다. 해제하시겠습니까?」 → 예: 모바일·이메일 수신 안내장을 우편(자택)으로 변경 후 해제 / 아니오·X·Esc: 팝업만 닫고 동의 유지 / v3.7: 안내장 받으실 곳의 휴대폰·이메일은 가려서 표시(010-****-5678, 이메일 아이디 앞 2자리)</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8231,6 +8231,33 @@
       <c r="E85" s="11" t="inlineStr">
         <is>
           <t>MY-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>안내장 수신설정: 안내장 받으실 곳 휴대폰·이메일 마스킹 표시</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>MY-02</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -3532,7 +3532,7 @@
       </c>
       <c r="J39" s="45" t="inlineStr">
         <is>
-          <t>계약 선택, 납입 회차, 납입방법(계좌출금·가상계좌) / 납입 방법이 가상계좌면 발급 은행 선택(iM뱅크·농협), 내 계좌 출금이면 출금 계좌 선택</t>
+          <t>계약 선택(여러 건·전체선택), 납입 회차, 납입방법(계좌출금·가상계좌) / 납입 방법이 가상계좌면 발급 은행 선택(iM뱅크·농협), 내 계좌 출금이면 출금 계좌 선택</t>
         </is>
       </c>
       <c r="K39" s="32" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="O39" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 출금 계좌 「다른 본인 계좌 등록」 선택 시 계좌 등록 레이어팝업(CM-09) — 계좌 확인(은행 조회) 후 등록, 등록한 계좌가 출금 계좌로 선택</t>
+          <t>v3.7: 출금 계좌 「다른 본인 계좌 등록」 선택 시 계좌 등록 레이어팝업(CM-09) — 계좌 확인(은행 조회) 후 등록, 등록한 계좌가 출금 계좌로 선택 / v3.7: 납입할 계약 여러 건 선택·[전체선택]/[전체해제] — 납입 보험료·선납 할인은 고른 계약 보험료 합계 기준, 입력 단계 위에 고른 계약 수·이름 표시, 확인 단계 「납입할 계약」에 이름(N건)</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8258,6 +8258,33 @@
       <c r="E86" s="11" t="inlineStr">
         <is>
           <t>MY-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>보험료 납입 관리: 납입할 계약 여러 건 선택·전체선택, 고른 계약 보험료 합계로 납입</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>PM-01</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -3527,7 +3527,7 @@
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>납입 대상 회차, 미납·연체 여부, 납입금액, 선납 할인</t>
+          <t>계약별 납입 상태(연체·정상)·납입 방식·최종 납입일, 납입 대상 회차, 납입금액, 선납 할인</t>
         </is>
       </c>
       <c r="J39" s="45" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="O39" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 출금 계좌 「다른 본인 계좌 등록」 선택 시 계좌 등록 레이어팝업(CM-09) — 계좌 확인(은행 조회) 후 등록, 등록한 계좌가 출금 계좌로 선택 / v3.7: 납입할 계약 여러 건 선택·[전체선택]/[전체해제] — 납입 보험료·선납 할인은 고른 계약 보험료 합계 기준, 입력 단계 위에 고른 계약 수·이름 표시, 확인 단계 「납입할 계약」에 이름(N건)</t>
+          <t>v3.7: 출금 계좌 「다른 본인 계좌 등록」 선택 시 계좌 등록 레이어팝업(CM-09) — 계좌 확인(은행 조회) 후 등록, 등록한 계좌가 출금 계좌로 선택 / v3.7: 납입할 계약 여러 건 선택·[전체선택]/[전체해제] — 납입 보험료·선납 할인은 고른 계약 보험료 합계 기준, 입력 단계 위에 고른 계약 수·이름 표시, 확인 단계 「납입할 계약」에 이름(N건) / v3.7: 계약 카드에 납입 상태 「연체」·「정상」과 납입 방식·최종 납입일 표시 — 연체 판단: 월납은 직전 납입 후 1개월 초과, 선납(3·6·12개월 등)은 선납 기간 초과, 연납은 직전 연보험료 납입 후 12개월 초과</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8283,6 +8283,33 @@
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>PM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>보험료 납입 관리: 계약 카드에 납입 상태(연체·정상)와 납입 방식·최종 납입일 표시</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
         <is>
           <t>PM-01</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -5976,7 +5976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5993,6 +5993,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -8312,6 +8313,33 @@
       <c r="E88" s="11" t="inlineStr">
         <is>
           <t>PM-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>하단 이용 안내: 금융소비자보호·위법계약해지요구권 회사 홈페이지 링크 추가(새 창)</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>공통</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -857,6 +857,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2594,7 +2595,11 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O26" s="10" t="n"/>
+      <c r="O26" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 표 머리글(연금유형·연간 예상액·월 환산·보증기간) 가운데 정렬</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -5976,7 +5981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5993,7 +5998,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -8340,6 +8344,33 @@
       <c r="E89" s="11" t="inlineStr">
         <is>
           <t>공통</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>미래예상연금액 조회: 표 머리글 가운데 정렬</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>CT-07</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -857,7 +857,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5981,7 +5980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8371,6 +8370,33 @@
       <c r="E90" s="11" t="inlineStr">
         <is>
           <t>CT-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>표 정렬 통일(표가 있는 모든 화면): 머리글 가운데, 금액 칸 오른쪽, 그 외 가운데 (보험금 청구사항 안내 표는 행 머리글 안내라 왼쪽 유지)</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>공통</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -5980,7 +5980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8397,6 +8397,33 @@
       <c r="E91" s="11" t="inlineStr">
         <is>
           <t>공통</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>조회 목록 모바일 카드: 두 번째 열이 오른쪽 금액과 같은 열이면 제목을 열 이름으로(금액 중복 제거) — 연금지급내역 「지급금액」·미래예상연금액 「연간 예상액」·변액보험 펀드 「편입비율」</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>CT-05·CT-07·CT-03</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -857,6 +857,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2744,7 +2745,11 @@
           <t>없음</t>
         </is>
       </c>
-      <c r="O28" s="10" t="n"/>
+      <c r="O28" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 상세 내용의 파일 항목은 PDF 버튼(모바일 카드 목록에서도 내려받기)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -5980,7 +5985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8424,6 +8429,33 @@
       <c r="E92" s="11" t="inlineStr">
         <is>
           <t>CT-05·CT-07·CT-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>전자서명계약서류 조회: 상세 내용 파일 항목을 PDF 버튼으로(모바일 내려받기), 안내장 발송내역 열람 항목도 같이</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>CT-09·MY-07</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -5044,7 +5044,11 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O59" s="10" t="n"/>
+      <c r="O59" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -5117,7 +5121,11 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O60" s="10" t="n"/>
+      <c r="O60" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -5190,7 +5198,11 @@
           <t>없음</t>
         </is>
       </c>
-      <c r="O61" s="10" t="n"/>
+      <c r="O61" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -5263,7 +5275,11 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O62" s="10" t="n"/>
+      <c r="O62" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5336,7 +5352,11 @@
           <t>없음</t>
         </is>
       </c>
-      <c r="O63" s="10" t="n"/>
+      <c r="O63" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5409,7 +5429,11 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O64" s="20" t="n"/>
+      <c r="O64" s="20" t="inlineStr">
+        <is>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -5985,7 +6009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8456,6 +8480,33 @@
       <c r="E93" s="11" t="inlineStr">
         <is>
           <t>CT-09·MY-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>증명서 발급: 발급 완료 후 [완료] 버튼은 발급 화면으로 복귀(기존: 메인)</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>CF-01~06</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -5046,7 +5046,7 @@
       </c>
       <c r="O59" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀</t>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급]</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="O60" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀</t>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급]</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="O61" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀</t>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급]</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="O62" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀</t>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급]</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="O63" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀</t>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급]</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="O64" s="20" t="inlineStr">
         <is>
-          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀</t>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급]</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8505,6 +8505,33 @@
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>CF-01~06</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>증명서 발급: 발급 조건 화면 [취소] 버튼 삭제([발급하기]만), 발급 완료 [다시 발급] → [추가 발급]</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
         <is>
           <t>CF-01~06</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -2824,7 +2824,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=미성년 자녀만 가능(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현) / v3.7: 사고 유형 질병·재해·기타로 변경, 사고일 다음에 사고장소(초진병원) 필수 입력과 사고(발생경위) 여러 줄 입력(안내: 육하원칙, 예: 오늘 계단을 급하게 내려가다 발목을 접지름) 추가, 기존 병원명(선택) 항목은 사고장소(초진병원)로 대체</t>
+          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=미성년 자녀만 가능(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현) / v3.7: 사고 유형 질병·재해·기타로 변경, 사고일 다음에 사고장소(초진병원) 필수 입력과 사고(발생경위) 여러 줄 입력(안내: 육하원칙, 예: 오늘 계단을 급하게 내려가다 발목을 접지름) 추가, 기존 병원명(선택) 항목은 사고장소(초진병원)로 대체 / v3.7: 사고 유형 「기타」 선택 시 오른쪽 직접 입력칸(기타를 골라야 입력 가능·필수, 확인 단계 「기타(입력값)」, 모바일은 다음 줄)</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8534,6 +8534,33 @@
       <c r="E95" s="11" t="inlineStr">
         <is>
           <t>CF-01~06</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>보험금 청구: 사고 유형 「기타」 선택 시 오른쪽에 사고 유형 직접 입력</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>PY-01</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -2799,7 +2799,7 @@
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>청구 종류, 피보험자(청구 종류에 맞는 선택지), 사고유형(질병·재해·기타), 청구내용, 사고일, 사고장소(초진병원, 필수), 사고 발생경위(육하원칙, 선택), 초진일, 수령계좌, 증빙 이미지</t>
+          <t>청구 종류, 피보험자(청구 종류에 맞는 선택지), 사고유형(질병·재해·기타), 청구내용(사망·장해·진단·입원·수술·통원·치아·실손의료비), 사고일, 사고장소(초진병원, 필수), 사고 발생경위(육하원칙, 선택), 초진일, 수령계좌, 증빙 이미지</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=미성년 자녀만 가능(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현) / v3.7: 사고 유형 질병·재해·기타로 변경, 사고일 다음에 사고장소(초진병원) 필수 입력과 사고(발생경위) 여러 줄 입력(안내: 육하원칙, 예: 오늘 계단을 급하게 내려가다 발목을 접지름) 추가, 기존 병원명(선택) 항목은 사고장소(초진병원)로 대체 / v3.7: 사고 유형 「기타」 선택 시 오른쪽 직접 입력칸(기타를 골라야 입력 가능·필수, 확인 단계 「기타(입력값)」, 모바일은 다음 줄)</t>
+          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=미성년 자녀만 가능(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현) / v3.7: 사고 유형 질병·재해·기타로 변경, 사고일 다음에 사고장소(초진병원) 필수 입력과 사고(발생경위) 여러 줄 입력(안내: 육하원칙, 예: 오늘 계단을 급하게 내려가다 발목을 접지름) 추가, 기존 병원명(선택) 항목은 사고장소(초진병원)로 대체 / v3.7: 사고 유형 「기타」 선택 시 오른쪽 직접 입력칸(기타를 골라야 입력 가능·필수, 확인 단계 「기타(입력값)」, 모바일은 다음 줄) / v3.7: 청구 내용 선택지 사망·장해·진단·입원·수술·통원·치아·실손의료비</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8559,6 +8559,33 @@
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>PY-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>보험금 청구: 청구 내용 선택지 변경(사망·장해·진단·입원·수술·통원·치아·실손의료비)</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
         <is>
           <t>PY-01</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -2799,7 +2799,7 @@
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>청구 종류, 피보험자(청구 종류에 맞는 선택지), 사고유형(질병·재해·기타), 청구내용(사망·장해·진단·입원·수술·통원·치아·실손의료비), 사고일, 사고장소(초진병원, 필수), 사고 발생경위(육하원칙, 선택), 초진일, 수령계좌, 증빙 이미지</t>
+          <t>청구 종류, 피보험자(청구 종류에 맞는 선택지), 사고유형(질병·재해·기타), 청구내용(사망·장해·진단·입원·수술·통원·치아·실손의료비), 사고일(초진일), 사고장소(초진병원, 필수), 사고(발생경위/치료내용, 육하원칙, 필수), 초진일, 수령계좌, 증빙 이미지</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=미성년 자녀만 가능(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현) / v3.7: 사고 유형 질병·재해·기타로 변경, 사고일 다음에 사고장소(초진병원) 필수 입력과 사고(발생경위) 여러 줄 입력(안내: 육하원칙, 예: 오늘 계단을 급하게 내려가다 발목을 접지름) 추가, 기존 병원명(선택) 항목은 사고장소(초진병원)로 대체 / v3.7: 사고 유형 「기타」 선택 시 오른쪽 직접 입력칸(기타를 골라야 입력 가능·필수, 확인 단계 「기타(입력값)」, 모바일은 다음 줄) / v3.7: 청구 내용 선택지 사망·장해·진단·입원·수술·통원·치아·실손의료비</t>
+          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=미성년 자녀만 가능(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현) / v3.7: 사고 유형 질병·재해·기타로 변경, 사고일 다음에 사고장소(초진병원) 필수 입력과 사고(발생경위) 여러 줄 입력(안내: 육하원칙, 예: 오늘 계단을 급하게 내려가다 발목을 접지름) 추가, 기존 병원명(선택) 항목은 사고장소(초진병원)로 대체 / v3.7: 사고 유형 「기타」 선택 시 오른쪽 직접 입력칸(기타를 골라야 입력 가능·필수, 확인 단계 「기타(입력값)」, 모바일은 다음 줄) / v3.7: 청구 내용 선택지 사망·장해·진단·입원·수술·통원·치아·실손의료비 / v3.7: 사고일(발병일) → 사고일(초진일), 사고(발생경위) → 사고(발생경위/치료내용)·필수</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8586,6 +8586,33 @@
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>PY-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>보험금 청구: 사고일(발병일) → 사고일(초진일), 사고(발생경위) → 사고(발생경위/치료내용) 필수 입력</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
         <is>
           <t>PY-01</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -2799,7 +2799,7 @@
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>청구 종류, 피보험자(청구 종류에 맞는 선택지), 사고유형(질병·재해·기타), 청구내용(사망·장해·진단·입원·수술·통원·치아·실손의료비), 사고일(초진일), 사고장소(초진병원, 필수), 사고(발생경위/치료내용, 육하원칙, 필수), 초진일, 수령계좌, 증빙 이미지</t>
+          <t>청구 종류, 피보험자(청구 종류에 맞는 선택지), 사고유형(질병·재해·기타), 청구내용(사망·장해·진단·입원·수술·통원·치아·실손의료비), 사고일(초진일), 사고장소(초진병원, 필수), 사고(발생경위/치료내용, 육하원칙, 필수), 수령계좌, 증빙 이미지</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="O29" s="11" t="inlineStr">
         <is>
-          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=미성년 자녀만 가능(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현) / v3.7: 사고 유형 질병·재해·기타로 변경, 사고일 다음에 사고장소(초진병원) 필수 입력과 사고(발생경위) 여러 줄 입력(안내: 육하원칙, 예: 오늘 계단을 급하게 내려가다 발목을 접지름) 추가, 기존 병원명(선택) 항목은 사고장소(초진병원)로 대체 / v3.7: 사고 유형 「기타」 선택 시 오른쪽 직접 입력칸(기타를 골라야 입력 가능·필수, 확인 단계 「기타(입력값)」, 모바일은 다음 줄) / v3.7: 청구 내용 선택지 사망·장해·진단·입원·수술·통원·치아·실손의료비 / v3.7: 사고일(발병일) → 사고일(초진일), 사고(발생경위) → 사고(발생경위/치료내용)·필수</t>
+          <t>v3.2: 피보험자가 본인이 아니면 피보험자 동의서(미성년 자녀는 법정대리인 확인서) 제출 안내 / v3.7: 계약 선택 단계 삭제 — 첫 단계 「안내」(청구사항 안내 표·청구 종류 탭) → 입력 → 확인 → 인증 → 완료. 청구 종류별 피보험자: 본인=본인, 자녀=미성년 자녀만 가능(법정대리인 확인서), 수익자=배우자·자녀(피보험자 동의서 또는 사망진단서·가족관계증명서). 구비서류 「사고보험금 청구서류」(CS-01) 바로가기. 이용 가능 시간(08:00~23:00)은 안내만(시간 제한 미구현) / v3.7: 사고 유형 질병·재해·기타로 변경, 사고일 다음에 사고장소(초진병원) 필수 입력과 사고(발생경위) 여러 줄 입력(안내: 육하원칙, 예: 오늘 계단을 급하게 내려가다 발목을 접지름) 추가, 기존 병원명(선택) 항목은 사고장소(초진병원)로 대체 / v3.7: 사고 유형 「기타」 선택 시 오른쪽 직접 입력칸(기타를 골라야 입력 가능·필수, 확인 단계 「기타(입력값)」, 모바일은 다음 줄) / v3.7: 청구 내용 선택지 사망·장해·진단·입원·수술·통원·치아·실손의료비 / v3.7: 사고일(발병일) → 사고일(초진일), 사고(발생경위) → 사고(발생경위/치료내용)·필수 / v3.7: 초진일 항목 삭제(사고일(초진일)로 통합)</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8613,6 +8613,33 @@
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>PY-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>삭제</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>보험금 청구: 초진일 항목 삭제(사고일(초진일)로 통합)</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
         <is>
           <t>PY-01</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -857,7 +857,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -6009,7 +6008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8642,6 +8641,33 @@
       <c r="E99" s="11" t="inlineStr">
         <is>
           <t>PY-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>새로고침 시 브라우저의 이전 스크롤 위치 복원 대신 메인 맨 위에서 시작</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>공통</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -857,6 +857,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5045,7 +5046,7 @@
       </c>
       <c r="O59" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급]</t>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급] / v3.7: 발급 완료 [추가 발급]·[완료] 버튼 같은 크기</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5123,7 @@
       </c>
       <c r="O60" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급]</t>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급] / v3.7: 발급 완료 [추가 발급]·[완료] 버튼 같은 크기</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5200,7 @@
       </c>
       <c r="O61" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급]</t>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급] / v3.7: 발급 완료 [추가 발급]·[완료] 버튼 같은 크기</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5277,7 @@
       </c>
       <c r="O62" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급]</t>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급] / v3.7: 발급 완료 [추가 발급]·[완료] 버튼 같은 크기</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5354,7 @@
       </c>
       <c r="O63" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급]</t>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급] / v3.7: 발급 완료 [추가 발급]·[완료] 버튼 같은 크기</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5431,7 @@
       </c>
       <c r="O64" s="20" t="inlineStr">
         <is>
-          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급]</t>
+          <t>v3.7: 발급 완료 후 [완료]는 메인이 아닌 발급 화면으로 복귀 / v3.7: 발급 조건 화면은 [발급하기] 버튼만(취소 삭제), 발급 완료 화면 [다시 발급] → [추가 발급] / v3.7: 발급 완료 [추가 발급]·[완료] 버튼 같은 크기</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8668,6 +8669,33 @@
       <c r="E100" s="11" t="inlineStr">
         <is>
           <t>공통</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>증명서 발급: 발급 완료 [추가 발급]·[완료] 버튼 크기 동일</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>CF-01~06</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -4825,7 +4825,11 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O56" s="10" t="n"/>
+      <c r="O56" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 상환 구분 「전액 상환」 선택 시 상환 금액에 현재 잔액 자동 입력·고정(빠른 금액 버튼 비활성), 다른 구분으로 바꾸면 비움</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -6009,7 +6013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8696,6 +8700,33 @@
       <c r="E101" s="11" t="inlineStr">
         <is>
           <t>CF-01~06</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>보험계약대출 상환/이자납입: 전액 상환 선택 시 상환 금액에 현재 잔액 자동 입력</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>LN-04</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -4827,7 +4827,7 @@
       </c>
       <c r="O56" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 상환 구분 「전액 상환」 선택 시 상환 금액에 현재 잔액 자동 입력·고정(빠른 금액 버튼 비활성), 다른 구분으로 바꾸면 비움</t>
+          <t>v3.7: 상환 구분 「전액 상환」 선택 시 상환 금액에 현재 잔액 자동 입력·고정(빠른 금액 버튼 비활성), 다른 구분으로 바꾸면 비움 / v3.7: 상환 구분 「이자만 납입」 선택 시 상환 금액 0원 고정</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8725,6 +8725,33 @@
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>LN-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>보험계약대출 상환/이자납입: 이자만 납입 선택 시 상환 금액 0원 고정</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
         <is>
           <t>LN-04</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -4797,7 +4797,7 @@
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>대출 잔액, 미납 이자, 상환 후 잔액</t>
+          <t>대출 잔액, 경과 이자, 연체 이자, 상환 원금, 출금 금액, 상환 후 잔액</t>
         </is>
       </c>
       <c r="J56" s="13" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="O56" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 상환 구분 「전액 상환」 선택 시 상환 금액에 현재 잔액 자동 입력·고정(빠른 금액 버튼 비활성), 다른 구분으로 바꾸면 비움 / v3.7: 상환 구분 「이자만 납입」 선택 시 상환 금액 0원 고정</t>
+          <t>v3.7: 상환 구분 「전액 상환」 선택 시 상환 금액에 현재 잔액 자동 입력·고정(빠른 금액 버튼 비활성), 다른 구분으로 바꾸면 비움 / v3.7: 상환 구분 「이자만 납입」 선택 시 상환 금액 0원 고정 / v3.7: 계산 결과에 연체 이자 표시(경과 이자 다음, 출금 금액에 포함, 샘플 0원)</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8752,6 +8752,33 @@
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>LN-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>보험계약대출 상환/이자납입: 계산 결과에 연체 이자 표시(출금 금액에 포함)</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
         <is>
           <t>LN-04</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -4827,7 +4827,7 @@
       </c>
       <c r="O56" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 상환 구분 「전액 상환」 선택 시 상환 금액에 현재 잔액 자동 입력·고정(빠른 금액 버튼 비활성), 다른 구분으로 바꾸면 비움 / v3.7: 상환 구분 「이자만 납입」 선택 시 상환 금액 0원 고정 / v3.7: 계산 결과에 연체 이자 표시(경과 이자 다음, 출금 금액에 포함, 샘플 0원)</t>
+          <t>v3.7: 상환 구분 「전액 상환」 선택 시 상환 금액에 현재 잔액 자동 입력·고정(빠른 금액 버튼 비활성), 다른 구분으로 바꾸면 비움 / v3.7: 상환 구분 「이자만 납입」 선택 시 상환 금액 0원 고정 / v3.7: 계산 결과에 연체 이자 표시(경과 이자 다음, 출금 금액에 포함, 샘플 0원) / v3.7: 시연용 연체 대출 1건 추가((무)iM 튼튼 어린이보험, 잔액 1,500,000원, 이자 2개월 미납·연체 이자 18,450원) — 대출 카드에 정상/연체 표시, 계산·상환 금액 최대·전액 상환 자동 금액은 고른 대출 기준</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8779,6 +8779,33 @@
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>LN-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>보험계약대출 상환/이자납입: 시연용 연체 대출 1건(연체 이자 출금 금액 포함), 대출 카드 정상/연체 표시</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
         <is>
           <t>LN-04</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -4677,7 +4677,7 @@
       </c>
       <c r="O54" s="10" t="inlineStr">
         <is>
-          <t>v3.1: 신청금액이 대출 가능금액보다 적으면 대출이율이 낮은 계약부터 순서대로 배정(계약별 가능금액까지 채운 뒤 다음 계약)</t>
+          <t>v3.1: 신청금액이 대출 가능금액보다 적으면 대출이율이 낮은 계약부터 순서대로 배정(계약별 가능금액까지 채운 뒤 다음 계약) / v3.7: 대출금액 배정 표시 문구 「배정 합계」 → 「대출금 합계」</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8808,6 +8808,33 @@
       <c r="E105" s="11" t="inlineStr">
         <is>
           <t>LN-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>보험계약대출 신청: 「배정 합계」 → 「대출금 합계」</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>LN-02</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -4677,7 +4677,7 @@
       </c>
       <c r="O54" s="10" t="inlineStr">
         <is>
-          <t>v3.1: 신청금액이 대출 가능금액보다 적으면 대출이율이 낮은 계약부터 순서대로 배정(계약별 가능금액까지 채운 뒤 다음 계약) / v3.7: 대출금액 배정 표시 문구 「배정 합계」 → 「대출금 합계」</t>
+          <t>v3.1: 신청금액이 대출 가능금액보다 적으면 대출이율이 낮은 계약부터 순서대로 배정(계약별 가능금액까지 채운 뒤 다음 계약) / v3.7: 대출금액 배정 표시 문구 「배정 합계」 → 「대출금 합계」 / v3.7: 대출 신청금액은 대출 가능금액 합계를 넘어 입력 불가(넘게 입력하면 합계로 맞춤)</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8833,6 +8833,33 @@
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>LN-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>보험계약대출 신청: 대출 신청금액은 대출 가능금액 합계를 넘어 입력 불가</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
         <is>
           <t>LN-02</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -857,7 +857,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4767,7 +4766,7 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>보험계약대출</t>
+          <t>보험계약대출 관리</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -4827,7 +4826,7 @@
       </c>
       <c r="O56" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 상환 구분 「전액 상환」 선택 시 상환 금액에 현재 잔액 자동 입력·고정(빠른 금액 버튼 비활성), 다른 구분으로 바꾸면 비움 / v3.7: 상환 구분 「이자만 납입」 선택 시 상환 금액 0원 고정 / v3.7: 계산 결과에 연체 이자 표시(경과 이자 다음, 출금 금액에 포함, 샘플 0원) / v3.7: 시연용 연체 대출 1건 추가((무)iM 튼튼 어린이보험, 잔액 1,500,000원, 이자 2개월 미납·연체 이자 18,450원) — 대출 카드에 정상/연체 표시, 계산·상환 금액 최대·전액 상환 자동 금액은 고른 대출 기준</t>
+          <t>v3.7: 상환 구분 「전액 상환」 선택 시 상환 금액에 현재 잔액 자동 입력·고정(빠른 금액 버튼 비활성), 다른 구분으로 바꾸면 비움 / v3.7: 상환 구분 「이자만 납입」 선택 시 상환 금액 0원 고정 / v3.7: 계산 결과에 연체 이자 표시(경과 이자 다음, 출금 금액에 포함, 샘플 0원) / v3.7: 시연용 연체 대출 1건 추가((무)iM 튼튼 어린이보험, 잔액 1,500,000원, 이자 2개월 미납·연체 이자 18,450원) — 대출 카드에 정상/연체 표시, 계산·상환 금액 최대·전액 상환 자동 금액은 고른 대출 기준 / v3.7: 메뉴 위치 보험계약대출 → 보험계약대출 관리 첫 메뉴로 이동</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8862,6 +8861,33 @@
       <c r="E107" s="11" t="inlineStr">
         <is>
           <t>LN-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>보험계약대출 상환/이자납입: 메뉴 위치 보험계약대출 → 보험계약대출 관리 첫 메뉴로 이동</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>LN-04</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -4843,7 +4843,7 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>보험계약대출</t>
+          <t>보험계약대출 관리</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -4901,7 +4901,11 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O57" s="10" t="n"/>
+      <c r="O57" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 메뉴 위치 보험계약대출 → 보험계약대출 관리(보험계약대출 상환/이자납입 다음)로 이동</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -6012,7 +6016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8888,6 +8892,33 @@
       <c r="E108" s="11" t="inlineStr">
         <is>
           <t>LN-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>보험계약대출 정액분할상환: 메뉴 위치 보험계약대출 → 보험계약대출 관리(보험계약대출 상환/이자납입 다음)로 이동</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>LN-05</t>
         </is>
       </c>
     </row>
